--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_furn_home_furnishings.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_furn_home_furnishings.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.2359890327922372</v>
+        <v>0.2354568591135359</v>
       </c>
       <c r="C2">
-        <v>9.427652999778337</v>
+        <v>9.355893480743994</v>
       </c>
       <c r="D2">
-        <v>8.588652999778336</v>
+        <v>8.607593480743994</v>
       </c>
       <c r="E2">
-        <v>-2.33</v>
+        <v>-2.2393</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.0907</v>
       </c>
       <c r="G2">
         <v>0.839</v>
@@ -1451,28 +1451,28 @@
         <v>2.99</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.00456221</v>
       </c>
       <c r="N2">
-        <v>2.99</v>
+        <v>2.98543779</v>
       </c>
       <c r="O2">
-        <v>0.7176</v>
+        <v>0.7165050696</v>
       </c>
       <c r="P2">
-        <v>2.2724</v>
+        <v>2.2689327204</v>
       </c>
       <c r="Q2">
-        <v>2.5424</v>
+        <v>2.5389327204</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.2359890327922372</v>
+        <v>0.2374490698116524</v>
       </c>
       <c r="T2">
-        <v>0.9344695036460948</v>
+        <v>0.9416432089266104</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>655.3841230456293</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.2354568591135359</v>
+        <v>0.2349246854348345</v>
       </c>
       <c r="C3">
-        <v>9.355893480743994</v>
+        <v>9.284217684896033</v>
       </c>
       <c r="D3">
-        <v>8.607593480743994</v>
+        <v>8.626617684896033</v>
       </c>
       <c r="E3">
-        <v>-2.2393</v>
+        <v>-2.1486</v>
       </c>
       <c r="F3">
-        <v>0.0907</v>
+        <v>0.1814</v>
       </c>
       <c r="G3">
         <v>0.839</v>
@@ -1533,28 +1533,28 @@
         <v>2.99</v>
       </c>
       <c r="M3">
-        <v>0.00456221</v>
+        <v>0.009124419999999999</v>
       </c>
       <c r="N3">
-        <v>2.98543779</v>
+        <v>2.98087558</v>
       </c>
       <c r="O3">
-        <v>0.7165050696</v>
+        <v>0.7154101392000001</v>
       </c>
       <c r="P3">
-        <v>2.2689327204</v>
+        <v>2.2654654408</v>
       </c>
       <c r="Q3">
-        <v>2.5389327204</v>
+        <v>2.535465440799999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.2374490698116524</v>
+        <v>0.2389389035049331</v>
       </c>
       <c r="T3">
-        <v>0.9416432089266104</v>
+        <v>0.9489633163557077</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>655.3841230456293</v>
+        <v>327.6920615228146</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.2349246854348345</v>
+        <v>0.2343925117561332</v>
       </c>
       <c r="C4">
-        <v>9.284217684896033</v>
+        <v>9.212626168590322</v>
       </c>
       <c r="D4">
-        <v>8.626617684896033</v>
+        <v>8.645726168590322</v>
       </c>
       <c r="E4">
-        <v>-2.1486</v>
+        <v>-2.0579</v>
       </c>
       <c r="F4">
-        <v>0.1814</v>
+        <v>0.2721</v>
       </c>
       <c r="G4">
         <v>0.839</v>
@@ -1615,28 +1615,28 @@
         <v>2.99</v>
       </c>
       <c r="M4">
-        <v>0.009124419999999999</v>
+        <v>0.01368663</v>
       </c>
       <c r="N4">
-        <v>2.98087558</v>
+        <v>2.97631337</v>
       </c>
       <c r="O4">
-        <v>0.7154101392000001</v>
+        <v>0.7143152088</v>
       </c>
       <c r="P4">
-        <v>2.2654654408</v>
+        <v>2.2619981612</v>
       </c>
       <c r="Q4">
-        <v>2.535465440799999</v>
+        <v>2.5319981612</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.2389389035049331</v>
+        <v>0.240459455418694</v>
       </c>
       <c r="T4">
-        <v>0.9489633163557077</v>
+        <v>0.9564343538348897</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>327.6920615228146</v>
+        <v>218.4613743485431</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.2343925117561332</v>
+        <v>0.2338603380774317</v>
       </c>
       <c r="C5">
-        <v>9.212626168590322</v>
+        <v>9.141119493123133</v>
       </c>
       <c r="D5">
-        <v>8.645726168590322</v>
+        <v>8.664919493123133</v>
       </c>
       <c r="E5">
-        <v>-2.0579</v>
+        <v>-1.9672</v>
       </c>
       <c r="F5">
-        <v>0.2721</v>
+        <v>0.3628</v>
       </c>
       <c r="G5">
         <v>0.839</v>
@@ -1697,28 +1697,28 @@
         <v>2.99</v>
       </c>
       <c r="M5">
-        <v>0.01368663</v>
+        <v>0.01824884</v>
       </c>
       <c r="N5">
-        <v>2.97631337</v>
+        <v>2.97175116</v>
       </c>
       <c r="O5">
-        <v>0.7143152088</v>
+        <v>0.7132202784</v>
       </c>
       <c r="P5">
-        <v>2.2619981612</v>
+        <v>2.2585308816</v>
       </c>
       <c r="Q5">
-        <v>2.5319981612</v>
+        <v>2.5285308816</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.240459455418694</v>
+        <v>0.2420116854973247</v>
       </c>
       <c r="T5">
-        <v>0.9564343538348897</v>
+        <v>0.9640610379282212</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>218.4613743485431</v>
+        <v>163.8460307614073</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.2338603380774317</v>
+        <v>0.2333281643987304</v>
       </c>
       <c r="C6">
-        <v>9.141119493123133</v>
+        <v>9.069698224786078</v>
       </c>
       <c r="D6">
-        <v>8.664919493123133</v>
+        <v>8.684198224786078</v>
       </c>
       <c r="E6">
-        <v>-1.9672</v>
+        <v>-1.8765</v>
       </c>
       <c r="F6">
-        <v>0.3628</v>
+        <v>0.4535</v>
       </c>
       <c r="G6">
         <v>0.839</v>
@@ -1779,28 +1779,28 @@
         <v>2.99</v>
       </c>
       <c r="M6">
-        <v>0.01824884</v>
+        <v>0.02281105</v>
       </c>
       <c r="N6">
-        <v>2.97175116</v>
+        <v>2.96718895</v>
       </c>
       <c r="O6">
-        <v>0.7132202784</v>
+        <v>0.712125348</v>
       </c>
       <c r="P6">
-        <v>2.2585308816</v>
+        <v>2.255063602</v>
       </c>
       <c r="Q6">
-        <v>2.5285308816</v>
+        <v>2.525063601999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.2420116854973247</v>
+        <v>0.2435965941039267</v>
       </c>
       <c r="T6">
-        <v>0.9640610379282212</v>
+        <v>0.9718482837919387</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>163.8460307614073</v>
+        <v>131.0768246091259</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.2333281643987304</v>
+        <v>0.232795990720029</v>
       </c>
       <c r="C7">
-        <v>9.069698224786078</v>
+        <v>8.998362934921829</v>
       </c>
       <c r="D7">
-        <v>8.684198224786078</v>
+        <v>8.703562934921829</v>
       </c>
       <c r="E7">
-        <v>-1.8765</v>
+        <v>-1.7858</v>
       </c>
       <c r="F7">
-        <v>0.4535</v>
+        <v>0.5442</v>
       </c>
       <c r="G7">
         <v>0.839</v>
@@ -1861,28 +1861,28 @@
         <v>2.99</v>
       </c>
       <c r="M7">
-        <v>0.02281105</v>
+        <v>0.02737326</v>
       </c>
       <c r="N7">
-        <v>2.96718895</v>
+        <v>2.96262674</v>
       </c>
       <c r="O7">
-        <v>0.712125348</v>
+        <v>0.7110304176</v>
       </c>
       <c r="P7">
-        <v>2.255063602</v>
+        <v>2.2515963224</v>
       </c>
       <c r="Q7">
-        <v>2.525063601999999</v>
+        <v>2.5215963224</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.2435965941039267</v>
+        <v>0.2452152241702436</v>
       </c>
       <c r="T7">
-        <v>0.9718482837919387</v>
+        <v>0.9798012157378628</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>131.0768246091259</v>
+        <v>109.2306871742715</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.232795990720029</v>
+        <v>0.2322638170413276</v>
       </c>
       <c r="C8">
-        <v>8.998362934921829</v>
+        <v>8.927114199980531</v>
       </c>
       <c r="D8">
-        <v>8.703562934921829</v>
+        <v>8.723014199980531</v>
       </c>
       <c r="E8">
-        <v>-1.7858</v>
+        <v>-1.6951</v>
       </c>
       <c r="F8">
-        <v>0.5442</v>
+        <v>0.6348999999999999</v>
       </c>
       <c r="G8">
         <v>0.839</v>
@@ -1943,28 +1943,28 @@
         <v>2.99</v>
       </c>
       <c r="M8">
-        <v>0.02737326</v>
+        <v>0.03193546999999999</v>
       </c>
       <c r="N8">
-        <v>2.96262674</v>
+        <v>2.95806453</v>
       </c>
       <c r="O8">
-        <v>0.7110304176</v>
+        <v>0.7099354872</v>
       </c>
       <c r="P8">
-        <v>2.2515963224</v>
+        <v>2.2481290428</v>
       </c>
       <c r="Q8">
-        <v>2.5215963224</v>
+        <v>2.5181290428</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.2452152241702436</v>
+        <v>0.2468686634852985</v>
       </c>
       <c r="T8">
-        <v>0.9798012157378628</v>
+        <v>0.987925178478323</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>109.2306871742715</v>
+        <v>93.62630329223276</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.2322638170413276</v>
+        <v>0.2317316433626262</v>
       </c>
       <c r="C9">
-        <v>8.927114199980531</v>
+        <v>8.855952601577036</v>
       </c>
       <c r="D9">
-        <v>8.723014199980531</v>
+        <v>8.742552601577035</v>
       </c>
       <c r="E9">
-        <v>-1.6951</v>
+        <v>-1.6044</v>
       </c>
       <c r="F9">
-        <v>0.6349000000000001</v>
+        <v>0.7256</v>
       </c>
       <c r="G9">
         <v>0.839</v>
@@ -2025,28 +2025,28 @@
         <v>2.99</v>
       </c>
       <c r="M9">
-        <v>0.03193547000000001</v>
+        <v>0.03649768</v>
       </c>
       <c r="N9">
-        <v>2.95806453</v>
+        <v>2.95350232</v>
       </c>
       <c r="O9">
-        <v>0.7099354872</v>
+        <v>0.7088405568</v>
       </c>
       <c r="P9">
-        <v>2.2481290428</v>
+        <v>2.2446617632</v>
       </c>
       <c r="Q9">
-        <v>2.5181290428</v>
+        <v>2.514661763199999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2468686634852985</v>
+        <v>0.2485580471332894</v>
       </c>
       <c r="T9">
-        <v>0.987925178478323</v>
+        <v>0.9962257491044453</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>93.62630329223272</v>
+        <v>81.92301538070366</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.2317316433626262</v>
+        <v>0.2311994696839249</v>
       </c>
       <c r="C10">
-        <v>8.855952601577036</v>
+        <v>8.784878726548838</v>
       </c>
       <c r="D10">
-        <v>8.742552601577035</v>
+        <v>8.762178726548838</v>
       </c>
       <c r="E10">
-        <v>-1.6044</v>
+        <v>-1.5137</v>
       </c>
       <c r="F10">
-        <v>0.7256</v>
+        <v>0.8163</v>
       </c>
       <c r="G10">
         <v>0.839</v>
@@ -2107,28 +2107,28 @@
         <v>2.99</v>
       </c>
       <c r="M10">
-        <v>0.03649768</v>
+        <v>0.04105989</v>
       </c>
       <c r="N10">
-        <v>2.95350232</v>
+        <v>2.94894011</v>
       </c>
       <c r="O10">
-        <v>0.7088405568</v>
+        <v>0.7077456264</v>
       </c>
       <c r="P10">
-        <v>2.2446617632</v>
+        <v>2.2411944836</v>
       </c>
       <c r="Q10">
-        <v>2.514661763199999</v>
+        <v>2.5111944836</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2485580471332894</v>
+        <v>0.2502845600922252</v>
       </c>
       <c r="T10">
-        <v>0.9962257491044453</v>
+        <v>1.004708749854219</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>81.92301538070366</v>
+        <v>72.82045811618102</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.2311994696839249</v>
+        <v>0.2306672960052235</v>
       </c>
       <c r="C11">
-        <v>8.784878726548838</v>
+        <v>8.713893167014861</v>
       </c>
       <c r="D11">
-        <v>8.762178726548838</v>
+        <v>8.781893167014861</v>
       </c>
       <c r="E11">
-        <v>-1.5137</v>
+        <v>-1.423</v>
       </c>
       <c r="F11">
-        <v>0.8163</v>
+        <v>0.9069999999999999</v>
       </c>
       <c r="G11">
         <v>0.839</v>
@@ -2189,28 +2189,28 @@
         <v>2.99</v>
       </c>
       <c r="M11">
-        <v>0.04105989</v>
+        <v>0.04562209999999999</v>
       </c>
       <c r="N11">
-        <v>2.94894011</v>
+        <v>2.9443779</v>
       </c>
       <c r="O11">
-        <v>0.7077456264</v>
+        <v>0.706650696</v>
       </c>
       <c r="P11">
-        <v>2.2411944836</v>
+        <v>2.237727204</v>
       </c>
       <c r="Q11">
-        <v>2.5111944836</v>
+        <v>2.507727204</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2502845600922252</v>
+        <v>0.2520494400058039</v>
       </c>
       <c r="T11">
-        <v>1.004708749854219</v>
+        <v>1.013380261731765</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>72.82045811618102</v>
+        <v>65.53841230456294</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.2306672960052235</v>
+        <v>0.2301351223265221</v>
       </c>
       <c r="C12">
-        <v>8.713893167014861</v>
+        <v>8.642996520434984</v>
       </c>
       <c r="D12">
-        <v>8.781893167014861</v>
+        <v>8.801696520434984</v>
       </c>
       <c r="E12">
-        <v>-1.423</v>
+        <v>-1.3323</v>
       </c>
       <c r="F12">
-        <v>0.907</v>
+        <v>0.9977</v>
       </c>
       <c r="G12">
         <v>0.839</v>
@@ -2271,28 +2271,28 @@
         <v>2.99</v>
       </c>
       <c r="M12">
-        <v>0.0456221</v>
+        <v>0.05018431</v>
       </c>
       <c r="N12">
-        <v>2.9443779</v>
+        <v>2.93981569</v>
       </c>
       <c r="O12">
-        <v>0.706650696</v>
+        <v>0.7055557656</v>
       </c>
       <c r="P12">
-        <v>2.237727204</v>
+        <v>2.2342599244</v>
       </c>
       <c r="Q12">
-        <v>2.507727204</v>
+        <v>2.504259924399999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2520494400058039</v>
+        <v>0.2538539801421597</v>
       </c>
       <c r="T12">
-        <v>1.013380261731765</v>
+        <v>1.022246639044762</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>65.53841230456293</v>
+        <v>59.58037482232994</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.2301351223265221</v>
+        <v>0.2296029486478207</v>
       </c>
       <c r="C13">
-        <v>8.642996520434984</v>
+        <v>8.572189389670404</v>
       </c>
       <c r="D13">
-        <v>8.801696520434984</v>
+        <v>8.821589389670404</v>
       </c>
       <c r="E13">
-        <v>-1.3323</v>
+        <v>-1.2416</v>
       </c>
       <c r="F13">
-        <v>0.9977</v>
+        <v>1.0884</v>
       </c>
       <c r="G13">
         <v>0.839</v>
@@ -2353,28 +2353,28 @@
         <v>2.99</v>
       </c>
       <c r="M13">
-        <v>0.05018431</v>
+        <v>0.05474652</v>
       </c>
       <c r="N13">
-        <v>2.93981569</v>
+        <v>2.93525348</v>
       </c>
       <c r="O13">
-        <v>0.7055557656</v>
+        <v>0.7044608352</v>
       </c>
       <c r="P13">
-        <v>2.2342599244</v>
+        <v>2.2307926448</v>
       </c>
       <c r="Q13">
-        <v>2.504259924399999</v>
+        <v>2.5007926448</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2538539801421597</v>
+        <v>0.2556995325543417</v>
       </c>
       <c r="T13">
-        <v>1.022246639044762</v>
+        <v>1.031314524933054</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>59.58037482232994</v>
+        <v>54.61534358713577</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.2296029486478207</v>
+        <v>0.2290707749691194</v>
       </c>
       <c r="C14">
-        <v>8.572189389670404</v>
+        <v>8.501472383044813</v>
       </c>
       <c r="D14">
-        <v>8.821589389670404</v>
+        <v>8.841572383044813</v>
       </c>
       <c r="E14">
-        <v>-1.2416</v>
+        <v>-1.1509</v>
       </c>
       <c r="F14">
-        <v>1.0884</v>
+        <v>1.1791</v>
       </c>
       <c r="G14">
         <v>0.839</v>
@@ -2435,28 +2435,28 @@
         <v>2.99</v>
       </c>
       <c r="M14">
-        <v>0.05474652</v>
+        <v>0.05930873</v>
       </c>
       <c r="N14">
-        <v>2.93525348</v>
+        <v>2.93069127</v>
       </c>
       <c r="O14">
-        <v>0.7044608352</v>
+        <v>0.7033659047999999</v>
       </c>
       <c r="P14">
-        <v>2.2307926448</v>
+        <v>2.2273253652</v>
       </c>
       <c r="Q14">
-        <v>2.5007926448</v>
+        <v>2.4973253652</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2556995325543417</v>
+        <v>0.2575875114587579</v>
       </c>
       <c r="T14">
-        <v>1.031314524933054</v>
+        <v>1.040590867968203</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>54.61534358713577</v>
+        <v>50.41416331120225</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.2290707749691194</v>
+        <v>0.228538601290418</v>
       </c>
       <c r="C15">
-        <v>8.501472383044813</v>
+        <v>8.430846114406403</v>
       </c>
       <c r="D15">
-        <v>8.841572383044813</v>
+        <v>8.861646114406403</v>
       </c>
       <c r="E15">
-        <v>-1.1509</v>
+        <v>-1.0602</v>
       </c>
       <c r="F15">
-        <v>1.1791</v>
+        <v>1.2698</v>
       </c>
       <c r="G15">
         <v>0.839</v>
@@ -2517,28 +2517,28 @@
         <v>2.99</v>
       </c>
       <c r="M15">
-        <v>0.05930873</v>
+        <v>0.06387094000000001</v>
       </c>
       <c r="N15">
-        <v>2.93069127</v>
+        <v>2.92612906</v>
       </c>
       <c r="O15">
-        <v>0.7033659047999999</v>
+        <v>0.7022709744</v>
       </c>
       <c r="P15">
-        <v>2.2273253652</v>
+        <v>2.2238580856</v>
       </c>
       <c r="Q15">
-        <v>2.4973253652</v>
+        <v>2.493858085599999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2575875114587579</v>
+        <v>0.2595193968493233</v>
       </c>
       <c r="T15">
-        <v>1.040590867968203</v>
+        <v>1.050082939911147</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>50.41416331120225</v>
+        <v>46.81315164611636</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.228538601290418</v>
+        <v>0.2280064276117167</v>
       </c>
       <c r="C16">
-        <v>8.430846114406403</v>
+        <v>8.360311203190742</v>
       </c>
       <c r="D16">
-        <v>8.861646114406403</v>
+        <v>8.881811203190741</v>
       </c>
       <c r="E16">
-        <v>-1.0602</v>
+        <v>-0.9694999999999998</v>
       </c>
       <c r="F16">
-        <v>1.2698</v>
+        <v>1.3605</v>
       </c>
       <c r="G16">
         <v>0.839</v>
@@ -2599,28 +2599,28 @@
         <v>2.99</v>
       </c>
       <c r="M16">
-        <v>0.06387094000000001</v>
+        <v>0.06843315000000001</v>
       </c>
       <c r="N16">
-        <v>2.92612906</v>
+        <v>2.92156685</v>
       </c>
       <c r="O16">
-        <v>0.7022709744</v>
+        <v>0.701176044</v>
       </c>
       <c r="P16">
-        <v>2.2238580856</v>
+        <v>2.220390806</v>
       </c>
       <c r="Q16">
-        <v>2.493858085599999</v>
+        <v>2.490390806</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2595193968493233</v>
+        <v>0.2614967383667255</v>
       </c>
       <c r="T16">
-        <v>1.050082939911147</v>
+        <v>1.059798354723336</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>46.81315164611636</v>
+        <v>43.6922748697086</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.2280064276117166</v>
+        <v>0.2274742539330153</v>
       </c>
       <c r="C17">
-        <v>8.360311203190744</v>
+        <v>8.289868274484457</v>
       </c>
       <c r="D17">
-        <v>8.881811203190743</v>
+        <v>8.902068274484456</v>
       </c>
       <c r="E17">
-        <v>-0.9695</v>
+        <v>-0.8788</v>
       </c>
       <c r="F17">
-        <v>1.3605</v>
+        <v>1.4512</v>
       </c>
       <c r="G17">
         <v>0.839</v>
@@ -2681,28 +2681,28 @@
         <v>2.99</v>
       </c>
       <c r="M17">
-        <v>0.06843315</v>
+        <v>0.07299536</v>
       </c>
       <c r="N17">
-        <v>2.92156685</v>
+        <v>2.91700464</v>
       </c>
       <c r="O17">
-        <v>0.701176044</v>
+        <v>0.7000811136</v>
       </c>
       <c r="P17">
-        <v>2.220390806</v>
+        <v>2.2169235264</v>
       </c>
       <c r="Q17">
-        <v>2.490390806</v>
+        <v>2.4869235264</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2614967383667254</v>
+        <v>0.2635211594440658</v>
       </c>
       <c r="T17">
-        <v>1.059798354723336</v>
+        <v>1.069745088935815</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>43.69227486970861</v>
+        <v>40.96150769035183</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.2274742539330153</v>
+        <v>0.2269420802543139</v>
       </c>
       <c r="C18">
-        <v>8.289868274484457</v>
+        <v>8.219517959089854</v>
       </c>
       <c r="D18">
-        <v>8.902068274484456</v>
+        <v>8.922417959089854</v>
       </c>
       <c r="E18">
-        <v>-0.8788</v>
+        <v>-0.7881</v>
       </c>
       <c r="F18">
-        <v>1.4512</v>
+        <v>1.5419</v>
       </c>
       <c r="G18">
         <v>0.839</v>
@@ -2763,28 +2763,28 @@
         <v>2.99</v>
       </c>
       <c r="M18">
-        <v>0.07299536</v>
+        <v>0.07755756999999999</v>
       </c>
       <c r="N18">
-        <v>2.91700464</v>
+        <v>2.91244243</v>
       </c>
       <c r="O18">
-        <v>0.7000811136</v>
+        <v>0.6989861831999999</v>
       </c>
       <c r="P18">
-        <v>2.2169235264</v>
+        <v>2.2134562468</v>
       </c>
       <c r="Q18">
-        <v>2.4869235264</v>
+        <v>2.483456246799999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2635211594440658</v>
+        <v>0.2655943617521855</v>
       </c>
       <c r="T18">
-        <v>1.069745088935815</v>
+        <v>1.079931503490764</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>40.96150769035183</v>
+        <v>38.5520072379782</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.2269420802543139</v>
+        <v>0.2264099065756126</v>
       </c>
       <c r="C19">
-        <v>8.219517959089854</v>
+        <v>8.14926089359038</v>
       </c>
       <c r="D19">
-        <v>8.922417959089854</v>
+        <v>8.94286089359038</v>
       </c>
       <c r="E19">
-        <v>-0.7881</v>
+        <v>-0.6973999999999998</v>
       </c>
       <c r="F19">
-        <v>1.5419</v>
+        <v>1.6326</v>
       </c>
       <c r="G19">
         <v>0.839</v>
@@ -2845,28 +2845,28 @@
         <v>2.99</v>
       </c>
       <c r="M19">
-        <v>0.07755756999999999</v>
+        <v>0.08211978</v>
       </c>
       <c r="N19">
-        <v>2.91244243</v>
+        <v>2.90788022</v>
       </c>
       <c r="O19">
-        <v>0.6989861831999999</v>
+        <v>0.6978912528</v>
       </c>
       <c r="P19">
-        <v>2.2134562468</v>
+        <v>2.2099889672</v>
       </c>
       <c r="Q19">
-        <v>2.483456246799999</v>
+        <v>2.4799889672</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2655943617521855</v>
+        <v>0.2677181299702592</v>
       </c>
       <c r="T19">
-        <v>1.079931503490764</v>
+        <v>1.0903663671812</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>38.5520072379782</v>
+        <v>36.41022905809051</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.2264099065756126</v>
+        <v>0.2258777328969112</v>
       </c>
       <c r="C20">
-        <v>8.14926089359038</v>
+        <v>8.079097720417012</v>
       </c>
       <c r="D20">
-        <v>8.94286089359038</v>
+        <v>8.963397720417012</v>
       </c>
       <c r="E20">
-        <v>-0.6974</v>
+        <v>-0.6067</v>
       </c>
       <c r="F20">
-        <v>1.6326</v>
+        <v>1.7233</v>
       </c>
       <c r="G20">
         <v>0.839</v>
@@ -2927,28 +2927,28 @@
         <v>2.99</v>
       </c>
       <c r="M20">
-        <v>0.08211978</v>
+        <v>0.08668199</v>
       </c>
       <c r="N20">
-        <v>2.90788022</v>
+        <v>2.90331801</v>
       </c>
       <c r="O20">
-        <v>0.6978912528</v>
+        <v>0.6967963224</v>
       </c>
       <c r="P20">
-        <v>2.2099889672</v>
+        <v>2.2065216876</v>
       </c>
       <c r="Q20">
-        <v>2.4799889672</v>
+        <v>2.4765216876</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2677181299702592</v>
+        <v>0.2698943369097669</v>
       </c>
       <c r="T20">
-        <v>1.090366367181199</v>
+        <v>1.101058881826954</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>36.41022905809051</v>
+        <v>34.49390121292785</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.2258777328969112</v>
+        <v>0.2253455592182098</v>
       </c>
       <c r="C21">
-        <v>8.079097720417012</v>
+        <v>8.009029087915549</v>
       </c>
       <c r="D21">
-        <v>8.963397720417012</v>
+        <v>8.984029087915548</v>
       </c>
       <c r="E21">
-        <v>-0.6067</v>
+        <v>-0.516</v>
       </c>
       <c r="F21">
-        <v>1.7233</v>
+        <v>1.814</v>
       </c>
       <c r="G21">
         <v>0.839</v>
@@ -3009,28 +3009,28 @@
         <v>2.99</v>
       </c>
       <c r="M21">
-        <v>0.08668199</v>
+        <v>0.0912442</v>
       </c>
       <c r="N21">
-        <v>2.90331801</v>
+        <v>2.8987558</v>
       </c>
       <c r="O21">
-        <v>0.6967963224</v>
+        <v>0.6957013919999999</v>
       </c>
       <c r="P21">
-        <v>2.2065216876</v>
+        <v>2.203054408</v>
       </c>
       <c r="Q21">
-        <v>2.4765216876</v>
+        <v>2.473054407999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2698943369097669</v>
+        <v>0.2721249490227622</v>
       </c>
       <c r="T21">
-        <v>1.101058881826954</v>
+        <v>1.112018709338853</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>34.49390121292785</v>
+        <v>32.76920615228146</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.2253455592182098</v>
+        <v>0.2248133855395085</v>
       </c>
       <c r="C22">
-        <v>8.009029087915549</v>
+        <v>7.939055650414836</v>
       </c>
       <c r="D22">
-        <v>8.984029087915548</v>
+        <v>9.004755650414836</v>
       </c>
       <c r="E22">
-        <v>-0.516</v>
+        <v>-0.4252999999999998</v>
       </c>
       <c r="F22">
-        <v>1.814</v>
+        <v>1.9047</v>
       </c>
       <c r="G22">
         <v>0.839</v>
@@ -3091,28 +3091,28 @@
         <v>2.99</v>
       </c>
       <c r="M22">
-        <v>0.0912442</v>
+        <v>0.09580641000000001</v>
       </c>
       <c r="N22">
-        <v>2.8987558</v>
+        <v>2.89419359</v>
       </c>
       <c r="O22">
-        <v>0.6957013919999999</v>
+        <v>0.6946064616000001</v>
       </c>
       <c r="P22">
-        <v>2.203054408</v>
+        <v>2.1995871284</v>
       </c>
       <c r="Q22">
-        <v>2.473054407999999</v>
+        <v>2.4695871284</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2721249490227622</v>
+        <v>0.2744120323284917</v>
       </c>
       <c r="T22">
-        <v>1.112018709338853</v>
+        <v>1.123256000838394</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>32.76920615228146</v>
+        <v>31.20876776407758</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.2248133855395084</v>
+        <v>0.2242812118608071</v>
       </c>
       <c r="C23">
-        <v>7.939055650414838</v>
+        <v>7.869178068295961</v>
       </c>
       <c r="D23">
-        <v>9.004755650414838</v>
+        <v>9.02557806829596</v>
       </c>
       <c r="E23">
-        <v>-0.4253</v>
+        <v>-0.3346</v>
       </c>
       <c r="F23">
-        <v>1.9047</v>
+        <v>1.9954</v>
       </c>
       <c r="G23">
         <v>0.839</v>
@@ -3173,28 +3173,28 @@
         <v>2.99</v>
       </c>
       <c r="M23">
-        <v>0.09580640999999999</v>
+        <v>0.10036862</v>
       </c>
       <c r="N23">
-        <v>2.89419359</v>
+        <v>2.88963138</v>
       </c>
       <c r="O23">
-        <v>0.6946064616000001</v>
+        <v>0.6935115312000001</v>
       </c>
       <c r="P23">
-        <v>2.1995871284</v>
+        <v>2.1961198488</v>
       </c>
       <c r="Q23">
-        <v>2.4695871284</v>
+        <v>2.4661198488</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2744120323284917</v>
+        <v>0.2767577587959065</v>
       </c>
       <c r="T23">
-        <v>1.123256000838394</v>
+        <v>1.134781428017412</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>31.20876776407759</v>
+        <v>29.79018741116497</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.2242812118608071</v>
+        <v>0.2237490381821057</v>
       </c>
       <c r="C24">
-        <v>7.869178068295961</v>
+        <v>7.799397008062368</v>
       </c>
       <c r="D24">
-        <v>9.02557806829596</v>
+        <v>9.046497008062367</v>
       </c>
       <c r="E24">
-        <v>-0.3346</v>
+        <v>-0.2439</v>
       </c>
       <c r="F24">
-        <v>1.9954</v>
+        <v>2.0861</v>
       </c>
       <c r="G24">
         <v>0.839</v>
@@ -3255,28 +3255,28 @@
         <v>2.99</v>
       </c>
       <c r="M24">
-        <v>0.10036862</v>
+        <v>0.10493083</v>
       </c>
       <c r="N24">
-        <v>2.88963138</v>
+        <v>2.88506917</v>
       </c>
       <c r="O24">
-        <v>0.6935115312000001</v>
+        <v>0.6924166008000001</v>
       </c>
       <c r="P24">
-        <v>2.1961198488</v>
+        <v>2.1926525692</v>
       </c>
       <c r="Q24">
-        <v>2.4661198488</v>
+        <v>2.4626525692</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2767577587959065</v>
+        <v>0.2791644132235139</v>
       </c>
       <c r="T24">
-        <v>1.134781428017412</v>
+        <v>1.146606216941338</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>29.79018741116497</v>
+        <v>28.4949618715491</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.2237490381821057</v>
+        <v>0.2232168645034044</v>
       </c>
       <c r="C25">
-        <v>7.799397008062368</v>
+        <v>7.729713142410976</v>
       </c>
       <c r="D25">
-        <v>9.046497008062367</v>
+        <v>9.067513142410975</v>
       </c>
       <c r="E25">
-        <v>-0.2439</v>
+        <v>-0.1532</v>
       </c>
       <c r="F25">
-        <v>2.0861</v>
+        <v>2.1768</v>
       </c>
       <c r="G25">
         <v>0.839</v>
@@ -3337,28 +3337,28 @@
         <v>2.99</v>
       </c>
       <c r="M25">
-        <v>0.10493083</v>
+        <v>0.10949304</v>
       </c>
       <c r="N25">
-        <v>2.88506917</v>
+        <v>2.88050696</v>
       </c>
       <c r="O25">
-        <v>0.6924166008000001</v>
+        <v>0.6913216704</v>
       </c>
       <c r="P25">
-        <v>2.1926525692</v>
+        <v>2.1891852896</v>
       </c>
       <c r="Q25">
-        <v>2.4626525692</v>
+        <v>2.4591852896</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2791644132235139</v>
+        <v>0.2816344006623742</v>
       </c>
       <c r="T25">
-        <v>1.146606216941338</v>
+        <v>1.158742184521158</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>28.4949618715491</v>
+        <v>27.30767179356789</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.2232168645034044</v>
+        <v>0.222684690824703</v>
       </c>
       <c r="C26">
-        <v>7.729713142410976</v>
+        <v>7.660127150304309</v>
       </c>
       <c r="D26">
-        <v>9.067513142410975</v>
+        <v>9.088627150304308</v>
       </c>
       <c r="E26">
-        <v>-0.1532</v>
+        <v>-0.0625</v>
       </c>
       <c r="F26">
-        <v>2.1768</v>
+        <v>2.2675</v>
       </c>
       <c r="G26">
         <v>0.839</v>
@@ -3419,28 +3419,28 @@
         <v>2.99</v>
       </c>
       <c r="M26">
-        <v>0.10949304</v>
+        <v>0.11405525</v>
       </c>
       <c r="N26">
-        <v>2.88050696</v>
+        <v>2.87594475</v>
       </c>
       <c r="O26">
-        <v>0.6913216704</v>
+        <v>0.6902267400000001</v>
       </c>
       <c r="P26">
-        <v>2.1891852896</v>
+        <v>2.18571801</v>
       </c>
       <c r="Q26">
-        <v>2.4591852896</v>
+        <v>2.45571801</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2816344006623742</v>
+        <v>0.2841702544329373</v>
       </c>
       <c r="T26">
-        <v>1.158742184521158</v>
+        <v>1.171201777903106</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>27.30767179356789</v>
+        <v>26.21536492182517</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.222684690824703</v>
+        <v>0.2221525171460016</v>
       </c>
       <c r="C27">
-        <v>7.660127150304309</v>
+        <v>7.590639717043585</v>
       </c>
       <c r="D27">
-        <v>9.088627150304308</v>
+        <v>9.109839717043585</v>
       </c>
       <c r="E27">
-        <v>-0.0625</v>
+        <v>0.0282</v>
       </c>
       <c r="F27">
-        <v>2.2675</v>
+        <v>2.3582</v>
       </c>
       <c r="G27">
         <v>0.839</v>
@@ -3501,28 +3501,28 @@
         <v>2.99</v>
       </c>
       <c r="M27">
-        <v>0.11405525</v>
+        <v>0.11861746</v>
       </c>
       <c r="N27">
-        <v>2.87594475</v>
+        <v>2.87138254</v>
       </c>
       <c r="O27">
-        <v>0.6902267400000001</v>
+        <v>0.6891318096000001</v>
       </c>
       <c r="P27">
-        <v>2.18571801</v>
+        <v>2.1822507304</v>
       </c>
       <c r="Q27">
-        <v>2.45571801</v>
+        <v>2.4522507304</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2841702544329373</v>
+        <v>0.286774644791894</v>
       </c>
       <c r="T27">
-        <v>1.171201777903106</v>
+        <v>1.183998117052133</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>26.21536492182517</v>
+        <v>25.20708165560113</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.2221525171460016</v>
+        <v>0.2216203434673002</v>
       </c>
       <c r="C28">
-        <v>7.590639717043585</v>
+        <v>7.521251534342877</v>
       </c>
       <c r="D28">
-        <v>9.109839717043585</v>
+        <v>9.131151534342877</v>
       </c>
       <c r="E28">
-        <v>0.0282</v>
+        <v>0.1189</v>
       </c>
       <c r="F28">
-        <v>2.3582</v>
+        <v>2.4489</v>
       </c>
       <c r="G28">
         <v>0.839</v>
@@ -3583,28 +3583,28 @@
         <v>2.99</v>
       </c>
       <c r="M28">
-        <v>0.11861746</v>
+        <v>0.12317967</v>
       </c>
       <c r="N28">
-        <v>2.87138254</v>
+        <v>2.86682033</v>
       </c>
       <c r="O28">
-        <v>0.6891318096000001</v>
+        <v>0.6880368792</v>
       </c>
       <c r="P28">
-        <v>2.1822507304</v>
+        <v>2.1787834508</v>
       </c>
       <c r="Q28">
-        <v>2.4522507304</v>
+        <v>2.4487834508</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.286774644791894</v>
+        <v>0.2894503883113702</v>
       </c>
       <c r="T28">
-        <v>1.183998117052133</v>
+        <v>1.197145040835381</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>25.20708165560113</v>
+        <v>24.27348603872701</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.2216203434673002</v>
+        <v>0.2210881697885988</v>
       </c>
       <c r="C29">
-        <v>7.521251534342877</v>
+        <v>7.451963300404303</v>
       </c>
       <c r="D29">
-        <v>9.131151534342877</v>
+        <v>9.152563300404303</v>
       </c>
       <c r="E29">
-        <v>0.1189</v>
+        <v>0.2096000000000005</v>
       </c>
       <c r="F29">
-        <v>2.4489</v>
+        <v>2.539600000000001</v>
       </c>
       <c r="G29">
         <v>0.839</v>
@@ -3665,28 +3665,28 @@
         <v>2.99</v>
       </c>
       <c r="M29">
-        <v>0.12317967</v>
+        <v>0.12774188</v>
       </c>
       <c r="N29">
-        <v>2.86682033</v>
+        <v>2.86225812</v>
       </c>
       <c r="O29">
-        <v>0.6880368792</v>
+        <v>0.6869419488</v>
       </c>
       <c r="P29">
-        <v>2.1787834508</v>
+        <v>2.1753161712</v>
       </c>
       <c r="Q29">
-        <v>2.4487834508</v>
+        <v>2.4453161712</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2894503883113702</v>
+        <v>0.2922004580397206</v>
       </c>
       <c r="T29">
-        <v>1.197145040835381</v>
+        <v>1.210657156945941</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>24.27348603872701</v>
+        <v>23.40657582305818</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.2210881697885988</v>
+        <v>0.2205559961098975</v>
       </c>
       <c r="C30">
-        <v>7.451963300404303</v>
+        <v>7.382775719994266</v>
       </c>
       <c r="D30">
-        <v>9.152563300404303</v>
+        <v>9.174075719994265</v>
       </c>
       <c r="E30">
-        <v>0.2096000000000005</v>
+        <v>0.3003000000000005</v>
       </c>
       <c r="F30">
-        <v>2.539600000000001</v>
+        <v>2.630300000000001</v>
       </c>
       <c r="G30">
         <v>0.839</v>
@@ -3747,28 +3747,28 @@
         <v>2.99</v>
       </c>
       <c r="M30">
-        <v>0.12774188</v>
+        <v>0.13230409</v>
       </c>
       <c r="N30">
-        <v>2.86225812</v>
+        <v>2.85769591</v>
       </c>
       <c r="O30">
-        <v>0.6869419488</v>
+        <v>0.6858470184000001</v>
       </c>
       <c r="P30">
-        <v>2.1753161712</v>
+        <v>2.1718488916</v>
       </c>
       <c r="Q30">
-        <v>2.4453161712</v>
+        <v>2.4418488916</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2922004580397206</v>
+        <v>0.2950279945209824</v>
       </c>
       <c r="T30">
-        <v>1.210657156945941</v>
+        <v>1.224549896045531</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>23.40657582305818</v>
+        <v>22.5994525188148</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.2205559961098975</v>
+        <v>0.2200238224311961</v>
       </c>
       <c r="C31">
-        <v>7.382775719994266</v>
+        <v>7.313689504520788</v>
       </c>
       <c r="D31">
-        <v>9.174075719994265</v>
+        <v>9.195689504520788</v>
       </c>
       <c r="E31">
-        <v>0.3003</v>
+        <v>0.391</v>
       </c>
       <c r="F31">
-        <v>2.6303</v>
+        <v>2.721</v>
       </c>
       <c r="G31">
         <v>0.839</v>
@@ -3829,28 +3829,28 @@
         <v>2.99</v>
       </c>
       <c r="M31">
-        <v>0.13230409</v>
+        <v>0.1368663</v>
       </c>
       <c r="N31">
-        <v>2.85769591</v>
+        <v>2.8531337</v>
       </c>
       <c r="O31">
-        <v>0.6858470184000001</v>
+        <v>0.6847520880000001</v>
       </c>
       <c r="P31">
-        <v>2.1718488916</v>
+        <v>2.168381612</v>
       </c>
       <c r="Q31">
-        <v>2.4418488916</v>
+        <v>2.438381612</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2950279945209824</v>
+        <v>0.2979363177588516</v>
       </c>
       <c r="T31">
-        <v>1.224549896045531</v>
+        <v>1.238839570547966</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>22.5994525188148</v>
+        <v>21.84613743485431</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.2200238224311961</v>
+        <v>0.2194916487524947</v>
       </c>
       <c r="C32">
-        <v>7.313689504520788</v>
+        <v>7.24470537211192</v>
       </c>
       <c r="D32">
-        <v>9.195689504520788</v>
+        <v>9.217405372111919</v>
       </c>
       <c r="E32">
-        <v>0.391</v>
+        <v>0.4817</v>
       </c>
       <c r="F32">
-        <v>2.721</v>
+        <v>2.8117</v>
       </c>
       <c r="G32">
         <v>0.839</v>
@@ -3911,28 +3911,28 @@
         <v>2.99</v>
       </c>
       <c r="M32">
-        <v>0.1368663</v>
+        <v>0.14142851</v>
       </c>
       <c r="N32">
-        <v>2.8531337</v>
+        <v>2.84857149</v>
       </c>
       <c r="O32">
-        <v>0.6847520880000001</v>
+        <v>0.6836571576</v>
       </c>
       <c r="P32">
-        <v>2.168381612</v>
+        <v>2.1649143324</v>
       </c>
       <c r="Q32">
-        <v>2.438381612</v>
+        <v>2.4349143324</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2979363177588516</v>
+        <v>0.3009289402210069</v>
       </c>
       <c r="T32">
-        <v>1.238839570547966</v>
+        <v>1.25354343851424</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>21.84613743485431</v>
+        <v>21.14142332405256</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.2194916487524947</v>
+        <v>0.2189594750737934</v>
       </c>
       <c r="C33">
-        <v>7.24470537211192</v>
+        <v>7.175824047695292</v>
       </c>
       <c r="D33">
-        <v>9.217405372111919</v>
+        <v>9.239224047695291</v>
       </c>
       <c r="E33">
-        <v>0.4817</v>
+        <v>0.5724</v>
       </c>
       <c r="F33">
-        <v>2.8117</v>
+        <v>2.9024</v>
       </c>
       <c r="G33">
         <v>0.839</v>
@@ -3993,28 +3993,28 @@
         <v>2.99</v>
       </c>
       <c r="M33">
-        <v>0.14142851</v>
+        <v>0.14599072</v>
       </c>
       <c r="N33">
-        <v>2.84857149</v>
+        <v>2.84400928</v>
       </c>
       <c r="O33">
-        <v>0.6836571576</v>
+        <v>0.6825622272</v>
       </c>
       <c r="P33">
-        <v>2.1649143324</v>
+        <v>2.1614470528</v>
       </c>
       <c r="Q33">
-        <v>2.4349143324</v>
+        <v>2.4314470528</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.3009289402210069</v>
+        <v>0.3040095809908727</v>
       </c>
       <c r="T33">
-        <v>1.25354343851424</v>
+        <v>1.268679773185404</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>21.14142332405256</v>
+        <v>20.48075384517592</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.2189594750737934</v>
+        <v>0.218427301395092</v>
       </c>
       <c r="C34">
-        <v>7.175824047695292</v>
+        <v>7.107046263078772</v>
       </c>
       <c r="D34">
-        <v>9.239224047695291</v>
+        <v>9.261146263078771</v>
       </c>
       <c r="E34">
-        <v>0.5724</v>
+        <v>0.6631</v>
       </c>
       <c r="F34">
-        <v>2.9024</v>
+        <v>2.9931</v>
       </c>
       <c r="G34">
         <v>0.839</v>
@@ -4075,28 +4075,28 @@
         <v>2.99</v>
       </c>
       <c r="M34">
-        <v>0.14599072</v>
+        <v>0.15055293</v>
       </c>
       <c r="N34">
-        <v>2.84400928</v>
+        <v>2.83944707</v>
       </c>
       <c r="O34">
-        <v>0.6825622272</v>
+        <v>0.6814672968000001</v>
       </c>
       <c r="P34">
-        <v>2.1614470528</v>
+        <v>2.1579797732</v>
       </c>
       <c r="Q34">
-        <v>2.4314470528</v>
+        <v>2.4279797732</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.3040095809908727</v>
+        <v>0.3071821811867045</v>
       </c>
       <c r="T34">
-        <v>1.268679773185404</v>
+        <v>1.284267938742275</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>20.48075384517592</v>
+        <v>19.86012494077664</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.218427301395092</v>
+        <v>0.2178951277163907</v>
       </c>
       <c r="C35">
-        <v>7.107046263078772</v>
+        <v>7.038372757032281</v>
       </c>
       <c r="D35">
-        <v>9.261146263078771</v>
+        <v>9.283172757032281</v>
       </c>
       <c r="E35">
-        <v>0.6631</v>
+        <v>0.7538</v>
       </c>
       <c r="F35">
-        <v>2.9931</v>
+        <v>3.0838</v>
       </c>
       <c r="G35">
         <v>0.839</v>
@@ -4157,28 +4157,28 @@
         <v>2.99</v>
       </c>
       <c r="M35">
-        <v>0.15055293</v>
+        <v>0.15511514</v>
       </c>
       <c r="N35">
-        <v>2.83944707</v>
+        <v>2.83488486</v>
       </c>
       <c r="O35">
-        <v>0.6814672968000001</v>
+        <v>0.6803723664000001</v>
       </c>
       <c r="P35">
-        <v>2.1579797732</v>
+        <v>2.1545124936</v>
       </c>
       <c r="Q35">
-        <v>2.4279797732</v>
+        <v>2.4245124936</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.3071821811867045</v>
+        <v>0.3104509207824101</v>
       </c>
       <c r="T35">
-        <v>1.284267938742275</v>
+        <v>1.300328472952384</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>19.86012494077664</v>
+        <v>19.2760036189891</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.2178951277163907</v>
+        <v>0.2173629540376892</v>
       </c>
       <c r="C36">
-        <v>7.038372757032281</v>
+        <v>6.969804275370803</v>
       </c>
       <c r="D36">
-        <v>9.283172757032281</v>
+        <v>9.305304275370803</v>
       </c>
       <c r="E36">
-        <v>0.7538</v>
+        <v>0.8445000000000005</v>
       </c>
       <c r="F36">
-        <v>3.0838</v>
+        <v>3.174500000000001</v>
       </c>
       <c r="G36">
         <v>0.839</v>
@@ -4239,28 +4239,28 @@
         <v>2.99</v>
       </c>
       <c r="M36">
-        <v>0.15511514</v>
+        <v>0.15967735</v>
       </c>
       <c r="N36">
-        <v>2.83488486</v>
+        <v>2.83032265</v>
       </c>
       <c r="O36">
-        <v>0.6803723664000001</v>
+        <v>0.679277436</v>
       </c>
       <c r="P36">
-        <v>2.1545124936</v>
+        <v>2.151045214</v>
       </c>
       <c r="Q36">
-        <v>2.4245124936</v>
+        <v>2.421045214</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.3104509207824101</v>
+        <v>0.3138202369810604</v>
       </c>
       <c r="T36">
-        <v>1.300328472952384</v>
+        <v>1.316883177445881</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>19.2760036189891</v>
+        <v>18.72526065844655</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.2173629540376892</v>
+        <v>0.2168307803589879</v>
       </c>
       <c r="C37">
-        <v>6.969804275370803</v>
+        <v>6.901341571038532</v>
       </c>
       <c r="D37">
-        <v>9.305304275370803</v>
+        <v>9.327541571038532</v>
       </c>
       <c r="E37">
-        <v>0.8445000000000005</v>
+        <v>0.9352000000000005</v>
       </c>
       <c r="F37">
-        <v>3.174500000000001</v>
+        <v>3.265200000000001</v>
       </c>
       <c r="G37">
         <v>0.839</v>
@@ -4321,28 +4321,28 @@
         <v>2.99</v>
       </c>
       <c r="M37">
-        <v>0.15967735</v>
+        <v>0.16423956</v>
       </c>
       <c r="N37">
-        <v>2.83032265</v>
+        <v>2.82576044</v>
       </c>
       <c r="O37">
-        <v>0.679277436</v>
+        <v>0.6781825056</v>
       </c>
       <c r="P37">
-        <v>2.151045214</v>
+        <v>2.1475779344</v>
       </c>
       <c r="Q37">
-        <v>2.421045214</v>
+        <v>2.4175779344</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.3138202369810604</v>
+        <v>0.3172948443109186</v>
       </c>
       <c r="T37">
-        <v>1.316883177445881</v>
+        <v>1.333955216454801</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>18.72526065844655</v>
+        <v>18.20511452904526</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.2168307803589879</v>
+        <v>0.2162986066802866</v>
       </c>
       <c r="C38">
-        <v>6.901341571038532</v>
+        <v>6.832985404194293</v>
       </c>
       <c r="D38">
-        <v>9.327541571038532</v>
+        <v>9.349885404194293</v>
       </c>
       <c r="E38">
-        <v>0.9352</v>
+        <v>1.0259</v>
       </c>
       <c r="F38">
-        <v>3.2652</v>
+        <v>3.3559</v>
       </c>
       <c r="G38">
         <v>0.839</v>
@@ -4403,28 +4403,28 @@
         <v>2.99</v>
       </c>
       <c r="M38">
-        <v>0.16423956</v>
+        <v>0.16880177</v>
       </c>
       <c r="N38">
-        <v>2.82576044</v>
+        <v>2.82119823</v>
       </c>
       <c r="O38">
-        <v>0.6781825056</v>
+        <v>0.6770875752000001</v>
       </c>
       <c r="P38">
-        <v>2.1475779344</v>
+        <v>2.1441106548</v>
       </c>
       <c r="Q38">
-        <v>2.4175779344</v>
+        <v>2.4141106548</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.3172948443109186</v>
+        <v>0.3208797566353755</v>
       </c>
       <c r="T38">
-        <v>1.3339552164548</v>
+        <v>1.351569224956066</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>18.20511452904526</v>
+        <v>17.71308440663863</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.2162986066802866</v>
+        <v>0.2157664330015852</v>
       </c>
       <c r="C39">
-        <v>6.832985404194293</v>
+        <v>6.76473654229814</v>
       </c>
       <c r="D39">
-        <v>9.349885404194293</v>
+        <v>9.37233654229814</v>
       </c>
       <c r="E39">
-        <v>1.0259</v>
+        <v>1.1166</v>
       </c>
       <c r="F39">
-        <v>3.3559</v>
+        <v>3.4466</v>
       </c>
       <c r="G39">
         <v>0.839</v>
@@ -4485,28 +4485,28 @@
         <v>2.99</v>
       </c>
       <c r="M39">
-        <v>0.16880177</v>
+        <v>0.17336398</v>
       </c>
       <c r="N39">
-        <v>2.82119823</v>
+        <v>2.81663602</v>
       </c>
       <c r="O39">
-        <v>0.6770875752000001</v>
+        <v>0.6759926448</v>
       </c>
       <c r="P39">
-        <v>2.1441106548</v>
+        <v>2.1406433752</v>
       </c>
       <c r="Q39">
-        <v>2.4141106548</v>
+        <v>2.4106433752</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.3208797566353755</v>
+        <v>0.3245803112928793</v>
       </c>
       <c r="T39">
-        <v>1.351569224956066</v>
+        <v>1.369751427279953</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>17.71308440663863</v>
+        <v>17.24695060646393</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2157664330015852</v>
+        <v>0.2152342593228838</v>
       </c>
       <c r="C40">
-        <v>6.76473654229814</v>
+        <v>6.696595760199232</v>
       </c>
       <c r="D40">
-        <v>9.37233654229814</v>
+        <v>9.394895760199232</v>
       </c>
       <c r="E40">
-        <v>1.1166</v>
+        <v>1.2073</v>
       </c>
       <c r="F40">
-        <v>3.4466</v>
+        <v>3.5373</v>
       </c>
       <c r="G40">
         <v>0.839</v>
@@ -4567,28 +4567,28 @@
         <v>2.99</v>
       </c>
       <c r="M40">
-        <v>0.17336398</v>
+        <v>0.17792619</v>
       </c>
       <c r="N40">
-        <v>2.81663602</v>
+        <v>2.81207381</v>
       </c>
       <c r="O40">
-        <v>0.6759926448</v>
+        <v>0.6748977144</v>
       </c>
       <c r="P40">
-        <v>2.1406433752</v>
+        <v>2.1371760956</v>
       </c>
       <c r="Q40">
-        <v>2.4106433752</v>
+        <v>2.4071760956</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.3245803112928793</v>
+        <v>0.328402195611285</v>
       </c>
       <c r="T40">
-        <v>1.369751427279953</v>
+        <v>1.388529767384951</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>17.24695060646393</v>
+        <v>16.80472110373409</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2152342593228838</v>
+        <v>0.2147020856441824</v>
       </c>
       <c r="C41">
-        <v>6.696595760199232</v>
+        <v>6.628563840224983</v>
       </c>
       <c r="D41">
-        <v>9.394895760199232</v>
+        <v>9.417563840224982</v>
       </c>
       <c r="E41">
-        <v>1.2073</v>
+        <v>1.298</v>
       </c>
       <c r="F41">
-        <v>3.5373</v>
+        <v>3.628</v>
       </c>
       <c r="G41">
         <v>0.839</v>
@@ -4649,28 +4649,28 @@
         <v>2.99</v>
       </c>
       <c r="M41">
-        <v>0.17792619</v>
+        <v>0.1824884</v>
       </c>
       <c r="N41">
-        <v>2.81207381</v>
+        <v>2.8075116</v>
       </c>
       <c r="O41">
-        <v>0.6748977144</v>
+        <v>0.673802784</v>
       </c>
       <c r="P41">
-        <v>2.1371760956</v>
+        <v>2.133708816</v>
       </c>
       <c r="Q41">
-        <v>2.4071760956</v>
+        <v>2.403708816</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.328402195611285</v>
+        <v>0.3323514760736374</v>
       </c>
       <c r="T41">
-        <v>1.388529767384951</v>
+        <v>1.407934052160116</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>16.80472110373409</v>
+        <v>16.38460307614073</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2147020856441824</v>
+        <v>0.214169911965481</v>
       </c>
       <c r="C42">
-        <v>6.628563840224983</v>
+        <v>6.560641572271493</v>
       </c>
       <c r="D42">
-        <v>9.417563840224982</v>
+        <v>9.440341572271493</v>
       </c>
       <c r="E42">
-        <v>1.298</v>
+        <v>1.3887</v>
       </c>
       <c r="F42">
-        <v>3.628</v>
+        <v>3.718700000000001</v>
       </c>
       <c r="G42">
         <v>0.839</v>
@@ -4731,28 +4731,28 @@
         <v>2.99</v>
       </c>
       <c r="M42">
-        <v>0.1824884</v>
+        <v>0.18705061</v>
       </c>
       <c r="N42">
-        <v>2.8075116</v>
+        <v>2.80294939</v>
       </c>
       <c r="O42">
-        <v>0.673802784</v>
+        <v>0.6727078536000001</v>
       </c>
       <c r="P42">
-        <v>2.133708816</v>
+        <v>2.1302415364</v>
       </c>
       <c r="Q42">
-        <v>2.403708816</v>
+        <v>2.4002415364</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.3323514760736374</v>
+        <v>0.3364346304499679</v>
       </c>
       <c r="T42">
-        <v>1.407934052160116</v>
+        <v>1.427996109300541</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>16.38460307614073</v>
+        <v>15.98497861086901</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.214169911965481</v>
+        <v>0.2136377382867797</v>
       </c>
       <c r="C43">
-        <v>6.560641572271493</v>
+        <v>6.492829753895286</v>
       </c>
       <c r="D43">
-        <v>9.440341572271493</v>
+        <v>9.463229753895286</v>
       </c>
       <c r="E43">
-        <v>1.3887</v>
+        <v>1.4794</v>
       </c>
       <c r="F43">
-        <v>3.718700000000001</v>
+        <v>3.809400000000001</v>
       </c>
       <c r="G43">
         <v>0.839</v>
@@ -4813,28 +4813,28 @@
         <v>2.99</v>
       </c>
       <c r="M43">
-        <v>0.18705061</v>
+        <v>0.19161282</v>
       </c>
       <c r="N43">
-        <v>2.80294939</v>
+        <v>2.79838718</v>
       </c>
       <c r="O43">
-        <v>0.6727078536000001</v>
+        <v>0.6716129232</v>
       </c>
       <c r="P43">
-        <v>2.1302415364</v>
+        <v>2.1267742568</v>
       </c>
       <c r="Q43">
-        <v>2.4002415364</v>
+        <v>2.3967742568</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.3364346304499679</v>
+        <v>0.3406585832530685</v>
       </c>
       <c r="T43">
-        <v>1.427996109300541</v>
+        <v>1.448749961514773</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>15.98497861086901</v>
+        <v>15.60438388203879</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2136377382867797</v>
+        <v>0.2131055646080783</v>
       </c>
       <c r="C44">
-        <v>6.492829753895284</v>
+        <v>6.42512919040643</v>
       </c>
       <c r="D44">
-        <v>9.463229753895284</v>
+        <v>9.48622919040643</v>
       </c>
       <c r="E44">
-        <v>1.4794</v>
+        <v>1.5701</v>
       </c>
       <c r="F44">
-        <v>3.8094</v>
+        <v>3.9001</v>
       </c>
       <c r="G44">
         <v>0.839</v>
@@ -4895,28 +4895,28 @@
         <v>2.99</v>
       </c>
       <c r="M44">
-        <v>0.19161282</v>
+        <v>0.19617503</v>
       </c>
       <c r="N44">
-        <v>2.79838718</v>
+        <v>2.79382497</v>
       </c>
       <c r="O44">
-        <v>0.6716129232</v>
+        <v>0.6705179928</v>
       </c>
       <c r="P44">
-        <v>2.1267742568</v>
+        <v>2.1233069772</v>
       </c>
       <c r="Q44">
-        <v>2.3967742568</v>
+        <v>2.3933069772</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.3406585832530685</v>
+        <v>0.3450307449264532</v>
       </c>
       <c r="T44">
-        <v>1.448749961514773</v>
+        <v>1.470232019069856</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>15.60438388203879</v>
+        <v>15.24149123361928</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2131055646080783</v>
+        <v>0.212573390929377</v>
       </c>
       <c r="C45">
-        <v>6.42512919040643</v>
+        <v>6.357540694962958</v>
       </c>
       <c r="D45">
-        <v>9.48622919040643</v>
+        <v>9.509340694962958</v>
       </c>
       <c r="E45">
-        <v>1.5701</v>
+        <v>1.6608</v>
       </c>
       <c r="F45">
-        <v>3.9001</v>
+        <v>3.9908</v>
       </c>
       <c r="G45">
         <v>0.839</v>
@@ -4977,28 +4977,28 @@
         <v>2.99</v>
       </c>
       <c r="M45">
-        <v>0.19617503</v>
+        <v>0.20073724</v>
       </c>
       <c r="N45">
-        <v>2.79382497</v>
+        <v>2.78926276</v>
       </c>
       <c r="O45">
-        <v>0.6705179928</v>
+        <v>0.6694230624</v>
       </c>
       <c r="P45">
-        <v>2.1233069772</v>
+        <v>2.1198396976</v>
       </c>
       <c r="Q45">
-        <v>2.3933069772</v>
+        <v>2.3898396976</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.3450307449264532</v>
+        <v>0.3495590552310303</v>
       </c>
       <c r="T45">
-        <v>1.470232019069856</v>
+        <v>1.492481292966191</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>15.24149123361928</v>
+        <v>14.89509370558248</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.212573390929377</v>
+        <v>0.2120412172506756</v>
       </c>
       <c r="C46">
-        <v>6.357540694962958</v>
+        <v>6.290065088666722</v>
       </c>
       <c r="D46">
-        <v>9.509340694962958</v>
+        <v>9.532565088666722</v>
       </c>
       <c r="E46">
-        <v>1.6608</v>
+        <v>1.7515</v>
       </c>
       <c r="F46">
-        <v>3.9908</v>
+        <v>4.0815</v>
       </c>
       <c r="G46">
         <v>0.839</v>
@@ -5059,28 +5059,28 @@
         <v>2.99</v>
       </c>
       <c r="M46">
-        <v>0.20073724</v>
+        <v>0.20529945</v>
       </c>
       <c r="N46">
-        <v>2.78926276</v>
+        <v>2.78470055</v>
       </c>
       <c r="O46">
-        <v>0.6694230624</v>
+        <v>0.668328132</v>
       </c>
       <c r="P46">
-        <v>2.1198396976</v>
+        <v>2.116372418</v>
       </c>
       <c r="Q46">
-        <v>2.3898396976</v>
+        <v>2.386372418</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.3495590552310303</v>
+        <v>0.3542520313648647</v>
       </c>
       <c r="T46">
-        <v>1.492481292966191</v>
+        <v>1.515539631367848</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>14.89509370558248</v>
+        <v>14.56409162323621</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2120412172506756</v>
+        <v>0.2115090435719742</v>
       </c>
       <c r="C47">
-        <v>6.290065088666722</v>
+        <v>6.222703200660622</v>
       </c>
       <c r="D47">
-        <v>9.532565088666722</v>
+        <v>9.555903200660621</v>
       </c>
       <c r="E47">
-        <v>1.7515</v>
+        <v>1.8422</v>
       </c>
       <c r="F47">
-        <v>4.0815</v>
+        <v>4.1722</v>
       </c>
       <c r="G47">
         <v>0.839</v>
@@ -5141,28 +5141,28 @@
         <v>2.99</v>
       </c>
       <c r="M47">
-        <v>0.20529945</v>
+        <v>0.20986166</v>
       </c>
       <c r="N47">
-        <v>2.78470055</v>
+        <v>2.78013834</v>
       </c>
       <c r="O47">
-        <v>0.668328132</v>
+        <v>0.6672332016</v>
       </c>
       <c r="P47">
-        <v>2.116372418</v>
+        <v>2.1129051384</v>
       </c>
       <c r="Q47">
-        <v>2.386372418</v>
+        <v>2.3829051384</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.3542520313648647</v>
+        <v>0.3591188214295819</v>
       </c>
       <c r="T47">
-        <v>1.515539631367848</v>
+        <v>1.5394519823029</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>14.56409162323621</v>
+        <v>14.24748093577455</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2115090435719742</v>
+        <v>0.2109768698932729</v>
       </c>
       <c r="C48">
-        <v>6.222703200660622</v>
+        <v>6.155455868227289</v>
       </c>
       <c r="D48">
-        <v>9.555903200660621</v>
+        <v>9.579355868227289</v>
       </c>
       <c r="E48">
-        <v>1.8422</v>
+        <v>1.9329</v>
       </c>
       <c r="F48">
-        <v>4.1722</v>
+        <v>4.2629</v>
       </c>
       <c r="G48">
         <v>0.839</v>
@@ -5223,28 +5223,28 @@
         <v>2.99</v>
       </c>
       <c r="M48">
-        <v>0.20986166</v>
+        <v>0.21442387</v>
       </c>
       <c r="N48">
-        <v>2.78013834</v>
+        <v>2.77557613</v>
       </c>
       <c r="O48">
-        <v>0.6672332016</v>
+        <v>0.6661382712</v>
       </c>
       <c r="P48">
-        <v>2.1129051384</v>
+        <v>2.1094378588</v>
       </c>
       <c r="Q48">
-        <v>2.3829051384</v>
+        <v>2.3794378588</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.3591188214295819</v>
+        <v>0.3641692639495714</v>
       </c>
       <c r="T48">
-        <v>1.5394519823029</v>
+        <v>1.564266686103425</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>14.24748093577455</v>
+        <v>13.94434304352403</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2109768698932729</v>
+        <v>0.2104446962145715</v>
       </c>
       <c r="C49">
-        <v>6.155455868227289</v>
+        <v>6.088323936889211</v>
       </c>
       <c r="D49">
-        <v>9.579355868227289</v>
+        <v>9.60292393688921</v>
       </c>
       <c r="E49">
-        <v>1.9329</v>
+        <v>2.0236</v>
       </c>
       <c r="F49">
-        <v>4.2629</v>
+        <v>4.3536</v>
       </c>
       <c r="G49">
         <v>0.839</v>
@@ -5305,28 +5305,28 @@
         <v>2.99</v>
       </c>
       <c r="M49">
-        <v>0.21442387</v>
+        <v>0.21898608</v>
       </c>
       <c r="N49">
-        <v>2.77557613</v>
+        <v>2.77101392</v>
       </c>
       <c r="O49">
-        <v>0.6661382712</v>
+        <v>0.6650433408</v>
       </c>
       <c r="P49">
-        <v>2.1094378588</v>
+        <v>2.1059705792</v>
       </c>
       <c r="Q49">
-        <v>2.3794378588</v>
+        <v>2.3759705792</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.3641692639495714</v>
+        <v>0.3694139542587913</v>
       </c>
       <c r="T49">
-        <v>1.564266686103425</v>
+        <v>1.590035801588586</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>13.94434304352403</v>
+        <v>13.65383589678394</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2104446962145715</v>
+        <v>0.2099125225358701</v>
       </c>
       <c r="C50">
-        <v>6.088323936889211</v>
+        <v>6.021308260510349</v>
       </c>
       <c r="D50">
-        <v>9.60292393688921</v>
+        <v>9.626608260510348</v>
       </c>
       <c r="E50">
-        <v>2.0236</v>
+        <v>2.1143</v>
       </c>
       <c r="F50">
-        <v>4.3536</v>
+        <v>4.4443</v>
       </c>
       <c r="G50">
         <v>0.839</v>
@@ -5387,28 +5387,28 @@
         <v>2.99</v>
       </c>
       <c r="M50">
-        <v>0.21898608</v>
+        <v>0.22354829</v>
       </c>
       <c r="N50">
-        <v>2.77101392</v>
+        <v>2.76645171</v>
       </c>
       <c r="O50">
-        <v>0.6650433408</v>
+        <v>0.6639484104</v>
       </c>
       <c r="P50">
-        <v>2.1059705792</v>
+        <v>2.1025032996</v>
       </c>
       <c r="Q50">
-        <v>2.3759705792</v>
+        <v>2.3725032996</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.3694139542587913</v>
+        <v>0.3748643186977845</v>
       </c>
       <c r="T50">
-        <v>1.590035801588586</v>
+        <v>1.616815470622184</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>13.65383589678394</v>
+        <v>13.37518618460468</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2099125225358701</v>
+        <v>0.2093803488571687</v>
       </c>
       <c r="C51">
-        <v>6.021308260510349</v>
+        <v>5.95440970139925</v>
       </c>
       <c r="D51">
-        <v>9.626608260510348</v>
+        <v>9.65040970139925</v>
       </c>
       <c r="E51">
-        <v>2.1143</v>
+        <v>2.205</v>
       </c>
       <c r="F51">
-        <v>4.4443</v>
+        <v>4.535</v>
       </c>
       <c r="G51">
         <v>0.839</v>
@@ -5469,28 +5469,28 @@
         <v>2.99</v>
       </c>
       <c r="M51">
-        <v>0.22354829</v>
+        <v>0.2281105</v>
       </c>
       <c r="N51">
-        <v>2.76645171</v>
+        <v>2.7618895</v>
       </c>
       <c r="O51">
-        <v>0.6639484104</v>
+        <v>0.66285348</v>
       </c>
       <c r="P51">
-        <v>2.1025032996</v>
+        <v>2.09903602</v>
       </c>
       <c r="Q51">
-        <v>2.3725032996</v>
+        <v>2.36903602</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.3748643186977845</v>
+        <v>0.3805326977143375</v>
       </c>
       <c r="T51">
-        <v>1.616815470622184</v>
+        <v>1.644666326417127</v>
       </c>
       <c r="U51">
         <v>0.0503</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>13.37518618460468</v>
+        <v>13.10768246091259</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2093803488571687</v>
+        <v>0.2094295751784674</v>
       </c>
       <c r="C52">
-        <v>5.95440970139925</v>
+        <v>5.861503117834294</v>
       </c>
       <c r="D52">
-        <v>9.65040970139925</v>
+        <v>9.648203117834294</v>
       </c>
       <c r="E52">
-        <v>2.205</v>
+        <v>2.2957</v>
       </c>
       <c r="F52">
-        <v>4.535</v>
+        <v>4.6257</v>
       </c>
       <c r="G52">
         <v>0.839</v>
@@ -5551,45 +5551,45 @@
         <v>2.99</v>
       </c>
       <c r="M52">
-        <v>0.2281105</v>
+        <v>0.23961126</v>
       </c>
       <c r="N52">
-        <v>2.7618895</v>
+        <v>2.75038874</v>
       </c>
       <c r="O52">
-        <v>0.66285348</v>
+        <v>0.6600932976</v>
       </c>
       <c r="P52">
-        <v>2.09903602</v>
+        <v>2.0902954424</v>
       </c>
       <c r="Q52">
-        <v>2.36903602</v>
+        <v>2.3602954424</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.3805326977143375</v>
+        <v>0.3864324391397294</v>
       </c>
       <c r="T52">
-        <v>1.644666326417127</v>
+        <v>1.673653951836353</v>
       </c>
       <c r="U52">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V52">
         <v>0.24</v>
       </c>
       <c r="W52">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y52">
-        <v>13.10768246091259</v>
+        <v>12.47854545733786</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2094295751784674</v>
+        <v>0.208908801499766</v>
       </c>
       <c r="C53">
-        <v>5.861503117834294</v>
+        <v>5.794198196889544</v>
       </c>
       <c r="D53">
-        <v>9.648203117834294</v>
+        <v>9.671598196889544</v>
       </c>
       <c r="E53">
-        <v>2.2957</v>
+        <v>2.3864</v>
       </c>
       <c r="F53">
-        <v>4.6257</v>
+        <v>4.7164</v>
       </c>
       <c r="G53">
         <v>0.839</v>
@@ -5633,28 +5633,28 @@
         <v>2.99</v>
       </c>
       <c r="M53">
-        <v>0.23961126</v>
+        <v>0.24430952</v>
       </c>
       <c r="N53">
-        <v>2.75038874</v>
+        <v>2.74569048</v>
       </c>
       <c r="O53">
-        <v>0.6600932976</v>
+        <v>0.6589657152</v>
       </c>
       <c r="P53">
-        <v>2.0902954424</v>
+        <v>2.0867247648</v>
       </c>
       <c r="Q53">
-        <v>2.3602954424</v>
+        <v>2.3567247648</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.3864324391397294</v>
+        <v>0.3925780031245126</v>
       </c>
       <c r="T53">
-        <v>1.673653951836353</v>
+        <v>1.70384939498138</v>
       </c>
       <c r="U53">
         <v>0.0518</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>12.47854545733786</v>
+        <v>12.23857342931213</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.208908801499766</v>
+        <v>0.2083880278210646</v>
       </c>
       <c r="C54">
-        <v>5.794198196889544</v>
+        <v>5.727007009064833</v>
       </c>
       <c r="D54">
-        <v>9.671598196889544</v>
+        <v>9.695107009064833</v>
       </c>
       <c r="E54">
-        <v>2.3864</v>
+        <v>2.4771</v>
       </c>
       <c r="F54">
-        <v>4.7164</v>
+        <v>4.8071</v>
       </c>
       <c r="G54">
         <v>0.839</v>
@@ -5715,28 +5715,28 @@
         <v>2.99</v>
       </c>
       <c r="M54">
-        <v>0.24430952</v>
+        <v>0.24900778</v>
       </c>
       <c r="N54">
-        <v>2.74569048</v>
+        <v>2.74099222</v>
       </c>
       <c r="O54">
-        <v>0.6589657152</v>
+        <v>0.6578381328</v>
       </c>
       <c r="P54">
-        <v>2.0867247648</v>
+        <v>2.083154087200001</v>
       </c>
       <c r="Q54">
-        <v>2.3567247648</v>
+        <v>2.3531540872</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.3925780031245126</v>
+        <v>0.3989850804703503</v>
       </c>
       <c r="T54">
-        <v>1.70384939498138</v>
+        <v>1.735329750600663</v>
       </c>
       <c r="U54">
         <v>0.0518</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>12.23857342931213</v>
+        <v>12.00765694951379</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2083880278210646</v>
+        <v>0.2078672541423633</v>
       </c>
       <c r="C55">
-        <v>5.727007009064833</v>
+        <v>5.659930385736331</v>
       </c>
       <c r="D55">
-        <v>9.695107009064833</v>
+        <v>9.718730385736331</v>
       </c>
       <c r="E55">
-        <v>2.4771</v>
+        <v>2.5678</v>
       </c>
       <c r="F55">
-        <v>4.8071</v>
+        <v>4.8978</v>
       </c>
       <c r="G55">
         <v>0.839</v>
@@ -5797,28 +5797,28 @@
         <v>2.99</v>
       </c>
       <c r="M55">
-        <v>0.24900778</v>
+        <v>0.25370604</v>
       </c>
       <c r="N55">
-        <v>2.74099222</v>
+        <v>2.73629396</v>
       </c>
       <c r="O55">
-        <v>0.6578381328</v>
+        <v>0.6567105504</v>
       </c>
       <c r="P55">
-        <v>2.083154087200001</v>
+        <v>2.0795834096</v>
       </c>
       <c r="Q55">
-        <v>2.3531540872</v>
+        <v>2.3495834096</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3989850804703503</v>
+        <v>0.4056707263964419</v>
       </c>
       <c r="T55">
-        <v>1.735329750600663</v>
+        <v>1.768178817333828</v>
       </c>
       <c r="U55">
         <v>0.0518</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>12.00765694951379</v>
+        <v>11.7852929319302</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2078672541423633</v>
+        <v>0.2073464804636619</v>
       </c>
       <c r="C56">
-        <v>5.659930385736331</v>
+        <v>5.592969166403035</v>
       </c>
       <c r="D56">
-        <v>9.718730385736331</v>
+        <v>9.742469166403035</v>
       </c>
       <c r="E56">
-        <v>2.5678</v>
+        <v>2.6585</v>
       </c>
       <c r="F56">
-        <v>4.8978</v>
+        <v>4.9885</v>
       </c>
       <c r="G56">
         <v>0.839</v>
@@ -5879,28 +5879,28 @@
         <v>2.99</v>
       </c>
       <c r="M56">
-        <v>0.25370604</v>
+        <v>0.2584043</v>
       </c>
       <c r="N56">
-        <v>2.73629396</v>
+        <v>2.7315957</v>
       </c>
       <c r="O56">
-        <v>0.6567105504</v>
+        <v>0.655582968</v>
       </c>
       <c r="P56">
-        <v>2.0795834096</v>
+        <v>2.076012732</v>
       </c>
       <c r="Q56">
-        <v>2.3495834096</v>
+        <v>2.346012732</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.4056707263964419</v>
+        <v>0.4126535121414709</v>
       </c>
       <c r="T56">
-        <v>1.768178817333828</v>
+        <v>1.802487842588468</v>
       </c>
       <c r="U56">
         <v>0.0518</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>11.7852929319302</v>
+        <v>11.57101487862238</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2073464804636619</v>
+        <v>0.2068257067849605</v>
       </c>
       <c r="C57">
-        <v>5.592969166403035</v>
+        <v>5.526124198786193</v>
       </c>
       <c r="D57">
-        <v>9.742469166403035</v>
+        <v>9.766324198786194</v>
       </c>
       <c r="E57">
-        <v>2.6585</v>
+        <v>2.749200000000001</v>
       </c>
       <c r="F57">
-        <v>4.9885</v>
+        <v>5.079200000000001</v>
       </c>
       <c r="G57">
         <v>0.839</v>
@@ -5961,28 +5961,28 @@
         <v>2.99</v>
       </c>
       <c r="M57">
-        <v>0.2584043</v>
+        <v>0.26310256</v>
       </c>
       <c r="N57">
-        <v>2.7315957</v>
+        <v>2.72689744</v>
       </c>
       <c r="O57">
-        <v>0.655582968</v>
+        <v>0.6544553856000001</v>
       </c>
       <c r="P57">
-        <v>2.076012732</v>
+        <v>2.0724420544</v>
       </c>
       <c r="Q57">
-        <v>2.346012732</v>
+        <v>2.3424420544</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.4126535121414709</v>
+        <v>0.4199536972385466</v>
       </c>
       <c r="T57">
-        <v>1.802487842588468</v>
+        <v>1.838356368991045</v>
       </c>
       <c r="U57">
         <v>0.0518</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>11.57101487862238</v>
+        <v>11.36438961293269</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2068257067849605</v>
+        <v>0.2063049331062592</v>
       </c>
       <c r="C58">
-        <v>5.526124198786193</v>
+        <v>5.45939633893022</v>
       </c>
       <c r="D58">
-        <v>9.766324198786194</v>
+        <v>9.79029633893022</v>
       </c>
       <c r="E58">
-        <v>2.749200000000001</v>
+        <v>2.839900000000001</v>
       </c>
       <c r="F58">
-        <v>5.079200000000001</v>
+        <v>5.169900000000001</v>
       </c>
       <c r="G58">
         <v>0.839</v>
@@ -6043,28 +6043,28 @@
         <v>2.99</v>
       </c>
       <c r="M58">
-        <v>0.26310256</v>
+        <v>0.2678008200000001</v>
       </c>
       <c r="N58">
-        <v>2.72689744</v>
+        <v>2.72219918</v>
       </c>
       <c r="O58">
-        <v>0.6544553856000001</v>
+        <v>0.6533278031999999</v>
       </c>
       <c r="P58">
-        <v>2.0724420544</v>
+        <v>2.0688713768</v>
       </c>
       <c r="Q58">
-        <v>2.3424420544</v>
+        <v>2.3388713768</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.4199536972385466</v>
+        <v>0.4275934258285097</v>
       </c>
       <c r="T58">
-        <v>1.838356368991045</v>
+        <v>1.875893198947231</v>
       </c>
       <c r="U58">
         <v>0.0518</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>11.36438961293269</v>
+        <v>11.16501435656545</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2063049331062592</v>
+        <v>0.2057841594275578</v>
       </c>
       <c r="C59">
-        <v>5.45939633893022</v>
+        <v>5.392786451305107</v>
       </c>
       <c r="D59">
-        <v>9.79029633893022</v>
+        <v>9.814386451305108</v>
       </c>
       <c r="E59">
-        <v>2.839900000000001</v>
+        <v>2.930600000000001</v>
       </c>
       <c r="F59">
-        <v>5.169900000000001</v>
+        <v>5.260600000000001</v>
       </c>
       <c r="G59">
         <v>0.839</v>
@@ -6125,28 +6125,28 @@
         <v>2.99</v>
       </c>
       <c r="M59">
-        <v>0.2678008200000001</v>
+        <v>0.2724990800000001</v>
       </c>
       <c r="N59">
-        <v>2.72219918</v>
+        <v>2.71750092</v>
       </c>
       <c r="O59">
-        <v>0.6533278031999999</v>
+        <v>0.6522002208</v>
       </c>
       <c r="P59">
-        <v>2.0688713768</v>
+        <v>2.0653006992</v>
       </c>
       <c r="Q59">
-        <v>2.3388713768</v>
+        <v>2.335300699199999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.4275934258285097</v>
+        <v>0.4355969510179947</v>
       </c>
       <c r="T59">
-        <v>1.875893198947231</v>
+        <v>1.915217496996568</v>
       </c>
       <c r="U59">
         <v>0.0518</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>11.16501435656545</v>
+        <v>10.97251410903846</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2057841594275578</v>
+        <v>0.2052633857488564</v>
       </c>
       <c r="C60">
-        <v>5.392786451305106</v>
+        <v>5.326295408910326</v>
       </c>
       <c r="D60">
-        <v>9.814386451305106</v>
+        <v>9.838595408910326</v>
       </c>
       <c r="E60">
-        <v>2.9306</v>
+        <v>3.0213</v>
       </c>
       <c r="F60">
-        <v>5.2606</v>
+        <v>5.3513</v>
       </c>
       <c r="G60">
         <v>0.839</v>
@@ -6207,28 +6207,28 @@
         <v>2.99</v>
       </c>
       <c r="M60">
-        <v>0.27249908</v>
+        <v>0.27719734</v>
       </c>
       <c r="N60">
-        <v>2.71750092</v>
+        <v>2.71280266</v>
       </c>
       <c r="O60">
-        <v>0.6522002208</v>
+        <v>0.6510726384000001</v>
       </c>
       <c r="P60">
-        <v>2.0653006992</v>
+        <v>2.0617300216</v>
       </c>
       <c r="Q60">
-        <v>2.335300699199999</v>
+        <v>2.3317300216</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.4355969510179947</v>
+        <v>0.4439908920703816</v>
       </c>
       <c r="T60">
-        <v>1.915217496996568</v>
+        <v>1.956460053487336</v>
       </c>
       <c r="U60">
         <v>0.0518</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>10.97251410903846</v>
+        <v>10.78653929363103</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2052633857488564</v>
+        <v>0.204742612070155</v>
       </c>
       <c r="C61">
-        <v>5.326295408910326</v>
+        <v>5.259924093380295</v>
       </c>
       <c r="D61">
-        <v>9.838595408910326</v>
+        <v>9.862924093380295</v>
       </c>
       <c r="E61">
-        <v>3.0213</v>
+        <v>3.112</v>
       </c>
       <c r="F61">
-        <v>5.3513</v>
+        <v>5.442</v>
       </c>
       <c r="G61">
         <v>0.839</v>
@@ -6289,28 +6289,28 @@
         <v>2.99</v>
       </c>
       <c r="M61">
-        <v>0.27719734</v>
+        <v>0.2818956</v>
       </c>
       <c r="N61">
-        <v>2.71280266</v>
+        <v>2.7081044</v>
       </c>
       <c r="O61">
-        <v>0.6510726384000001</v>
+        <v>0.6499450560000001</v>
       </c>
       <c r="P61">
-        <v>2.0617300216</v>
+        <v>2.058159344</v>
       </c>
       <c r="Q61">
-        <v>2.3317300216</v>
+        <v>2.328159344</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.4439908920703816</v>
+        <v>0.4528045301753876</v>
       </c>
       <c r="T61">
-        <v>1.956460053487336</v>
+        <v>1.999764737802643</v>
       </c>
       <c r="U61">
         <v>0.0518</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>10.78653929363103</v>
+        <v>10.60676363873718</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.204742612070155</v>
+        <v>0.2042218383914537</v>
       </c>
       <c r="C62">
-        <v>5.259924093380295</v>
+        <v>5.193673395091398</v>
       </c>
       <c r="D62">
-        <v>9.862924093380295</v>
+        <v>9.887373395091398</v>
       </c>
       <c r="E62">
-        <v>3.112</v>
+        <v>3.2027</v>
       </c>
       <c r="F62">
-        <v>5.442</v>
+        <v>5.5327</v>
       </c>
       <c r="G62">
         <v>0.839</v>
@@ -6371,28 +6371,28 @@
         <v>2.99</v>
       </c>
       <c r="M62">
-        <v>0.2818956</v>
+        <v>0.28659386</v>
       </c>
       <c r="N62">
-        <v>2.7081044</v>
+        <v>2.70340614</v>
       </c>
       <c r="O62">
-        <v>0.6499450560000001</v>
+        <v>0.6488174736000001</v>
       </c>
       <c r="P62">
-        <v>2.058159344</v>
+        <v>2.0545886664</v>
       </c>
       <c r="Q62">
-        <v>2.328159344</v>
+        <v>2.3245886664</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.4528045301753876</v>
+        <v>0.4620701497216761</v>
       </c>
       <c r="T62">
-        <v>1.999764737802643</v>
+        <v>2.045290175159761</v>
       </c>
       <c r="U62">
         <v>0.0518</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>10.60676363873718</v>
+        <v>10.43288226761034</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2042218383914537</v>
+        <v>0.2037010647127523</v>
       </c>
       <c r="C63">
-        <v>5.193673395091398</v>
+        <v>5.127544213270617</v>
       </c>
       <c r="D63">
-        <v>9.887373395091398</v>
+        <v>9.911944213270617</v>
       </c>
       <c r="E63">
-        <v>3.2027</v>
+        <v>3.2934</v>
       </c>
       <c r="F63">
-        <v>5.5327</v>
+        <v>5.6234</v>
       </c>
       <c r="G63">
         <v>0.839</v>
@@ -6453,28 +6453,28 @@
         <v>2.99</v>
       </c>
       <c r="M63">
-        <v>0.28659386</v>
+        <v>0.29129212</v>
       </c>
       <c r="N63">
-        <v>2.70340614</v>
+        <v>2.69870788</v>
       </c>
       <c r="O63">
-        <v>0.6488174736000001</v>
+        <v>0.6476898912</v>
       </c>
       <c r="P63">
-        <v>2.0545886664</v>
+        <v>2.0510179888</v>
       </c>
       <c r="Q63">
-        <v>2.3245886664</v>
+        <v>2.3210179888</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.4620701497216761</v>
+        <v>0.4718234334546114</v>
       </c>
       <c r="T63">
-        <v>2.045290175159761</v>
+        <v>2.093211688167253</v>
       </c>
       <c r="U63">
         <v>0.0518</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>10.43288226761034</v>
+        <v>10.26460997297146</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2037010647127523</v>
+        <v>0.2031802910340509</v>
       </c>
       <c r="C64">
-        <v>5.127544213270617</v>
+        <v>5.061537456105773</v>
       </c>
       <c r="D64">
-        <v>9.911944213270617</v>
+        <v>9.936637456105773</v>
       </c>
       <c r="E64">
-        <v>3.2934</v>
+        <v>3.3841</v>
       </c>
       <c r="F64">
-        <v>5.6234</v>
+        <v>5.7141</v>
       </c>
       <c r="G64">
         <v>0.839</v>
@@ -6535,28 +6535,28 @@
         <v>2.99</v>
       </c>
       <c r="M64">
-        <v>0.29129212</v>
+        <v>0.29599038</v>
       </c>
       <c r="N64">
-        <v>2.69870788</v>
+        <v>2.69400962</v>
       </c>
       <c r="O64">
-        <v>0.6476898912</v>
+        <v>0.6465623088</v>
       </c>
       <c r="P64">
-        <v>2.0510179888</v>
+        <v>2.0474473112</v>
       </c>
       <c r="Q64">
-        <v>2.3210179888</v>
+        <v>2.3174473112</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.4718234334546114</v>
+        <v>0.4821039217136511</v>
       </c>
       <c r="T64">
-        <v>2.093211688167253</v>
+        <v>2.143723553229203</v>
       </c>
       <c r="U64">
         <v>0.0518</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>10.26460997297146</v>
+        <v>10.10167965594017</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2031802910340509</v>
+        <v>0.2026595173553496</v>
       </c>
       <c r="C65">
-        <v>5.061537456105773</v>
+        <v>4.995654040857405</v>
       </c>
       <c r="D65">
-        <v>9.936637456105773</v>
+        <v>9.961454040857404</v>
       </c>
       <c r="E65">
-        <v>3.3841</v>
+        <v>3.4748</v>
       </c>
       <c r="F65">
-        <v>5.7141</v>
+        <v>5.8048</v>
       </c>
       <c r="G65">
         <v>0.839</v>
@@ -6617,28 +6617,28 @@
         <v>2.99</v>
       </c>
       <c r="M65">
-        <v>0.29599038</v>
+        <v>0.30068864</v>
       </c>
       <c r="N65">
-        <v>2.69400962</v>
+        <v>2.68931136</v>
       </c>
       <c r="O65">
-        <v>0.6465623088</v>
+        <v>0.6454347264</v>
       </c>
       <c r="P65">
-        <v>2.0474473112</v>
+        <v>2.0438766336</v>
       </c>
       <c r="Q65">
-        <v>2.3174473112</v>
+        <v>2.3138766336</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.4821039217136511</v>
+        <v>0.4929555482093044</v>
       </c>
       <c r="T65">
-        <v>2.143723553229203</v>
+        <v>2.197041633016819</v>
       </c>
       <c r="U65">
         <v>0.0518</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>10.10167965594017</v>
+        <v>9.943840911316105</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2026595173553496</v>
+        <v>0.2029785436766482</v>
       </c>
       <c r="C66">
-        <v>4.995654040857405</v>
+        <v>4.889736697156231</v>
       </c>
       <c r="D66">
-        <v>9.961454040857404</v>
+        <v>9.94623669715623</v>
       </c>
       <c r="E66">
-        <v>3.4748</v>
+        <v>3.5655</v>
       </c>
       <c r="F66">
-        <v>5.8048</v>
+        <v>5.8955</v>
       </c>
       <c r="G66">
         <v>0.839</v>
@@ -6699,45 +6699,45 @@
         <v>2.99</v>
       </c>
       <c r="M66">
-        <v>0.30068864</v>
+        <v>0.31540925</v>
       </c>
       <c r="N66">
-        <v>2.68931136</v>
+        <v>2.67459075</v>
       </c>
       <c r="O66">
-        <v>0.6454347264</v>
+        <v>0.64190178</v>
       </c>
       <c r="P66">
-        <v>2.0438766336</v>
+        <v>2.03268897</v>
       </c>
       <c r="Q66">
-        <v>2.3138766336</v>
+        <v>2.30268897</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.4929555482093044</v>
+        <v>0.5044272676475663</v>
       </c>
       <c r="T66">
-        <v>2.197041633016819</v>
+        <v>2.253406460220869</v>
       </c>
       <c r="U66">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V66">
         <v>0.24</v>
       </c>
       <c r="W66">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y66">
-        <v>9.943840911316105</v>
+        <v>9.479747344125132</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2029785436766482</v>
+        <v>0.2024706899979468</v>
       </c>
       <c r="C67">
-        <v>4.889736697156231</v>
+        <v>4.823282936916263</v>
       </c>
       <c r="D67">
-        <v>9.94623669715623</v>
+        <v>9.970482936916262</v>
       </c>
       <c r="E67">
-        <v>3.5655</v>
+        <v>3.6562</v>
       </c>
       <c r="F67">
-        <v>5.8955</v>
+        <v>5.9862</v>
       </c>
       <c r="G67">
         <v>0.839</v>
@@ -6781,28 +6781,28 @@
         <v>2.99</v>
       </c>
       <c r="M67">
-        <v>0.31540925</v>
+        <v>0.3202617</v>
       </c>
       <c r="N67">
-        <v>2.67459075</v>
+        <v>2.6697383</v>
       </c>
       <c r="O67">
-        <v>0.64190178</v>
+        <v>0.640737192</v>
       </c>
       <c r="P67">
-        <v>2.03268897</v>
+        <v>2.029001108</v>
       </c>
       <c r="Q67">
-        <v>2.30268897</v>
+        <v>2.299001108</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.5044272676475663</v>
+        <v>0.5165737941116083</v>
       </c>
       <c r="T67">
-        <v>2.253406460220869</v>
+        <v>2.313086865495745</v>
       </c>
       <c r="U67">
         <v>0.0535</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>9.479747344125132</v>
+        <v>9.336114808608086</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2024706899979468</v>
+        <v>0.2019628363192455</v>
       </c>
       <c r="C68">
-        <v>4.823282936916263</v>
+        <v>4.756947677121346</v>
       </c>
       <c r="D68">
-        <v>9.970482936916262</v>
+        <v>9.994847677121346</v>
       </c>
       <c r="E68">
-        <v>3.6562</v>
+        <v>3.7469</v>
       </c>
       <c r="F68">
-        <v>5.9862</v>
+        <v>6.0769</v>
       </c>
       <c r="G68">
         <v>0.839</v>
@@ -6863,28 +6863,28 @@
         <v>2.99</v>
       </c>
       <c r="M68">
-        <v>0.3202617</v>
+        <v>0.32511415</v>
       </c>
       <c r="N68">
-        <v>2.6697383</v>
+        <v>2.66488585</v>
       </c>
       <c r="O68">
-        <v>0.640737192</v>
+        <v>0.639572604</v>
       </c>
       <c r="P68">
-        <v>2.029001108</v>
+        <v>2.025313246</v>
       </c>
       <c r="Q68">
-        <v>2.299001108</v>
+        <v>2.295313246</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.5165737941116083</v>
+        <v>0.5294564736946833</v>
       </c>
       <c r="T68">
-        <v>2.313086865495745</v>
+        <v>2.376384265029706</v>
       </c>
       <c r="U68">
         <v>0.0535</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>9.336114808608086</v>
+        <v>9.196769811464682</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2019628363192455</v>
+        <v>0.2014549826405441</v>
       </c>
       <c r="C69">
-        <v>4.756947677121346</v>
+        <v>4.690731788633613</v>
       </c>
       <c r="D69">
-        <v>9.994847677121346</v>
+        <v>10.01933178863361</v>
       </c>
       <c r="E69">
-        <v>3.7469</v>
+        <v>3.8376</v>
       </c>
       <c r="F69">
-        <v>6.0769</v>
+        <v>6.1676</v>
       </c>
       <c r="G69">
         <v>0.839</v>
@@ -6945,28 +6945,28 @@
         <v>2.99</v>
       </c>
       <c r="M69">
-        <v>0.32511415</v>
+        <v>0.3299666</v>
       </c>
       <c r="N69">
-        <v>2.66488585</v>
+        <v>2.6600334</v>
       </c>
       <c r="O69">
-        <v>0.639572604</v>
+        <v>0.638408016</v>
       </c>
       <c r="P69">
-        <v>2.025313246</v>
+        <v>2.021625384</v>
       </c>
       <c r="Q69">
-        <v>2.295313246</v>
+        <v>2.291625384</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.5294564736946833</v>
+        <v>0.5431443207517003</v>
       </c>
       <c r="T69">
-        <v>2.376384265029706</v>
+        <v>2.443637752034538</v>
       </c>
       <c r="U69">
         <v>0.0535</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>9.196769811464682</v>
+        <v>9.061523196590201</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2014549826405441</v>
+        <v>0.2009471289618427</v>
       </c>
       <c r="C70">
-        <v>4.690731788633613</v>
+        <v>4.624636150869452</v>
       </c>
       <c r="D70">
-        <v>10.01933178863361</v>
+        <v>10.04393615086945</v>
       </c>
       <c r="E70">
-        <v>3.8376</v>
+        <v>3.928300000000001</v>
       </c>
       <c r="F70">
-        <v>6.1676</v>
+        <v>6.258300000000001</v>
       </c>
       <c r="G70">
         <v>0.839</v>
@@ -7027,28 +7027,28 @@
         <v>2.99</v>
       </c>
       <c r="M70">
-        <v>0.3299666</v>
+        <v>0.3348190500000001</v>
       </c>
       <c r="N70">
-        <v>2.6600334</v>
+        <v>2.65518095</v>
       </c>
       <c r="O70">
-        <v>0.638408016</v>
+        <v>0.637243428</v>
       </c>
       <c r="P70">
-        <v>2.021625384</v>
+        <v>2.017937522</v>
       </c>
       <c r="Q70">
-        <v>2.291625384</v>
+        <v>2.287937522</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.5431443207517003</v>
+        <v>0.5577152547156218</v>
       </c>
       <c r="T70">
-        <v>2.443637752034538</v>
+        <v>2.515230173684844</v>
       </c>
       <c r="U70">
         <v>0.0535</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>9.061523196590201</v>
+        <v>8.930196773451211</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2009471289618427</v>
+        <v>0.2004392752831413</v>
       </c>
       <c r="C71">
-        <v>4.624636150869452</v>
+        <v>4.558661651904823</v>
       </c>
       <c r="D71">
-        <v>10.04393615086945</v>
+        <v>10.06866165190482</v>
       </c>
       <c r="E71">
-        <v>3.928300000000001</v>
+        <v>4.019000000000001</v>
       </c>
       <c r="F71">
-        <v>6.258300000000001</v>
+        <v>6.349000000000001</v>
       </c>
       <c r="G71">
         <v>0.839</v>
@@ -7109,28 +7109,28 @@
         <v>2.99</v>
       </c>
       <c r="M71">
-        <v>0.3348190500000001</v>
+        <v>0.3396715000000001</v>
       </c>
       <c r="N71">
-        <v>2.65518095</v>
+        <v>2.6503285</v>
       </c>
       <c r="O71">
-        <v>0.637243428</v>
+        <v>0.63607884</v>
       </c>
       <c r="P71">
-        <v>2.017937522</v>
+        <v>2.01424966</v>
       </c>
       <c r="Q71">
-        <v>2.287937522</v>
+        <v>2.28424966</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.5577152547156218</v>
+        <v>0.5732575842771379</v>
       </c>
       <c r="T71">
-        <v>2.515230173684844</v>
+        <v>2.59159542344517</v>
       </c>
       <c r="U71">
         <v>0.0535</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>8.930196773451211</v>
+        <v>8.80262253383048</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2004392752831413</v>
+        <v>0.19993142160444</v>
       </c>
       <c r="C72">
-        <v>4.558661651904823</v>
+        <v>4.492809188582087</v>
       </c>
       <c r="D72">
-        <v>10.06866165190482</v>
+        <v>10.09350918858209</v>
       </c>
       <c r="E72">
-        <v>4.019000000000001</v>
+        <v>4.109700000000001</v>
       </c>
       <c r="F72">
-        <v>6.349000000000001</v>
+        <v>6.439700000000001</v>
       </c>
       <c r="G72">
         <v>0.839</v>
@@ -7191,28 +7191,28 @@
         <v>2.99</v>
       </c>
       <c r="M72">
-        <v>0.3396715000000001</v>
+        <v>0.3445239500000001</v>
       </c>
       <c r="N72">
-        <v>2.6503285</v>
+        <v>2.64547605</v>
       </c>
       <c r="O72">
-        <v>0.63607884</v>
+        <v>0.634914252</v>
       </c>
       <c r="P72">
-        <v>2.01424966</v>
+        <v>2.010561798</v>
       </c>
       <c r="Q72">
-        <v>2.28424966</v>
+        <v>2.280561798</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.5732575842771379</v>
+        <v>0.5898717986360001</v>
       </c>
       <c r="T72">
-        <v>2.59159542344517</v>
+        <v>2.673227242154485</v>
       </c>
       <c r="U72">
         <v>0.0535</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>8.80262253383048</v>
+        <v>8.678641934762444</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.19993142160444</v>
+        <v>0.1994235679257386</v>
       </c>
       <c r="C73">
-        <v>4.492809188582088</v>
+        <v>4.42707966661845</v>
       </c>
       <c r="D73">
-        <v>10.09350918858209</v>
+        <v>10.11847966661845</v>
       </c>
       <c r="E73">
-        <v>4.1097</v>
+        <v>4.2004</v>
       </c>
       <c r="F73">
-        <v>6.4397</v>
+        <v>6.5304</v>
       </c>
       <c r="G73">
         <v>0.839</v>
@@ -7273,28 +7273,28 @@
         <v>2.99</v>
       </c>
       <c r="M73">
-        <v>0.34452395</v>
+        <v>0.3493764</v>
       </c>
       <c r="N73">
-        <v>2.64547605</v>
+        <v>2.6406236</v>
       </c>
       <c r="O73">
-        <v>0.634914252</v>
+        <v>0.633749664</v>
       </c>
       <c r="P73">
-        <v>2.010561798</v>
+        <v>2.006873936</v>
       </c>
       <c r="Q73">
-        <v>2.280561798</v>
+        <v>2.276873935999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.5898717986359999</v>
+        <v>0.6076727425919235</v>
       </c>
       <c r="T73">
-        <v>2.673227242154484</v>
+        <v>2.76068990505732</v>
       </c>
       <c r="U73">
         <v>0.0535</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>8.678641934762446</v>
+        <v>8.558105241224077</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1994235679257386</v>
+        <v>0.1989157142470372</v>
       </c>
       <c r="C74">
-        <v>4.42707966661845</v>
+        <v>4.361474000716012</v>
       </c>
       <c r="D74">
-        <v>10.11847966661845</v>
+        <v>10.14357400071601</v>
       </c>
       <c r="E74">
-        <v>4.2004</v>
+        <v>4.2911</v>
       </c>
       <c r="F74">
-        <v>6.5304</v>
+        <v>6.6211</v>
       </c>
       <c r="G74">
         <v>0.839</v>
@@ -7355,28 +7355,28 @@
         <v>2.99</v>
       </c>
       <c r="M74">
-        <v>0.3493764</v>
+        <v>0.35422885</v>
       </c>
       <c r="N74">
-        <v>2.6406236</v>
+        <v>2.63577115</v>
       </c>
       <c r="O74">
-        <v>0.633749664</v>
+        <v>0.632585076</v>
       </c>
       <c r="P74">
-        <v>2.006873936</v>
+        <v>2.003186074</v>
       </c>
       <c r="Q74">
-        <v>2.276873935999999</v>
+        <v>2.273186074</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.6076727425919235</v>
+        <v>0.6267922749890268</v>
       </c>
       <c r="T74">
-        <v>2.76068990505732</v>
+        <v>2.854631283730737</v>
       </c>
       <c r="U74">
         <v>0.0535</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>8.558105241224077</v>
+        <v>8.440870922851147</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1989157142470372</v>
+        <v>0.1984078605683358</v>
       </c>
       <c r="C75">
-        <v>4.361474000716012</v>
+        <v>4.295993114673465</v>
       </c>
       <c r="D75">
-        <v>10.14357400071601</v>
+        <v>10.16879311467346</v>
       </c>
       <c r="E75">
-        <v>4.2911</v>
+        <v>4.3818</v>
       </c>
       <c r="F75">
-        <v>6.6211</v>
+        <v>6.7118</v>
       </c>
       <c r="G75">
         <v>0.839</v>
@@ -7437,28 +7437,28 @@
         <v>2.99</v>
       </c>
       <c r="M75">
-        <v>0.35422885</v>
+        <v>0.3590813</v>
       </c>
       <c r="N75">
-        <v>2.63577115</v>
+        <v>2.6309187</v>
       </c>
       <c r="O75">
-        <v>0.632585076</v>
+        <v>0.6314204879999999</v>
       </c>
       <c r="P75">
-        <v>2.003186074</v>
+        <v>1.999498212</v>
       </c>
       <c r="Q75">
-        <v>2.273186074</v>
+        <v>2.269498212</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.6267922749890268</v>
+        <v>0.6473825406474455</v>
       </c>
       <c r="T75">
-        <v>2.854631283730737</v>
+        <v>2.955798922302109</v>
       </c>
       <c r="U75">
         <v>0.0535</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>8.440870922851147</v>
+        <v>8.326805099569373</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1984078605683358</v>
+        <v>0.1979000068896345</v>
       </c>
       <c r="C76">
-        <v>4.295993114673465</v>
+        <v>4.230637941499442</v>
       </c>
       <c r="D76">
-        <v>10.16879311467346</v>
+        <v>10.19413794149944</v>
       </c>
       <c r="E76">
-        <v>4.3818</v>
+        <v>4.4725</v>
       </c>
       <c r="F76">
-        <v>6.7118</v>
+        <v>6.8025</v>
       </c>
       <c r="G76">
         <v>0.839</v>
@@ -7519,28 +7519,28 @@
         <v>2.99</v>
       </c>
       <c r="M76">
-        <v>0.3590813</v>
+        <v>0.36393375</v>
       </c>
       <c r="N76">
-        <v>2.6309187</v>
+        <v>2.62606625</v>
       </c>
       <c r="O76">
-        <v>0.6314204879999999</v>
+        <v>0.6302559</v>
       </c>
       <c r="P76">
-        <v>1.999498212</v>
+        <v>1.99581035</v>
       </c>
       <c r="Q76">
-        <v>2.269498212</v>
+        <v>2.26581035</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.6473825406474455</v>
+        <v>0.669620027558538</v>
       </c>
       <c r="T76">
-        <v>2.955798922302109</v>
+        <v>3.065059971959191</v>
       </c>
       <c r="U76">
         <v>0.0535</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>8.326805099569373</v>
+        <v>8.215781031575116</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1979000068896345</v>
+        <v>0.1973921532109331</v>
       </c>
       <c r="C77">
-        <v>4.230637941499442</v>
+        <v>4.165409423527599</v>
       </c>
       <c r="D77">
-        <v>10.19413794149944</v>
+        <v>10.2196094235276</v>
       </c>
       <c r="E77">
-        <v>4.4725</v>
+        <v>4.5632</v>
       </c>
       <c r="F77">
-        <v>6.8025</v>
+        <v>6.8932</v>
       </c>
       <c r="G77">
         <v>0.839</v>
@@ -7601,28 +7601,28 @@
         <v>2.99</v>
       </c>
       <c r="M77">
-        <v>0.36393375</v>
+        <v>0.3687862</v>
       </c>
       <c r="N77">
-        <v>2.62606625</v>
+        <v>2.6212138</v>
       </c>
       <c r="O77">
-        <v>0.6302559</v>
+        <v>0.629091312</v>
       </c>
       <c r="P77">
-        <v>1.99581035</v>
+        <v>1.992122488</v>
       </c>
       <c r="Q77">
-        <v>2.26581035</v>
+        <v>2.262122488</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.669620027558538</v>
+        <v>0.693710638378888</v>
       </c>
       <c r="T77">
-        <v>3.065059971959191</v>
+        <v>3.183426109087697</v>
       </c>
       <c r="U77">
         <v>0.0535</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>8.215781031575116</v>
+        <v>8.107678649580706</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1973921532109331</v>
+        <v>0.1968842995322318</v>
       </c>
       <c r="C78">
-        <v>4.165409423527599</v>
+        <v>4.100308512533385</v>
       </c>
       <c r="D78">
-        <v>10.2196094235276</v>
+        <v>10.24520851253338</v>
       </c>
       <c r="E78">
-        <v>4.5632</v>
+        <v>4.6539</v>
       </c>
       <c r="F78">
-        <v>6.8932</v>
+        <v>6.9839</v>
       </c>
       <c r="G78">
         <v>0.839</v>
@@ -7683,28 +7683,28 @@
         <v>2.99</v>
       </c>
       <c r="M78">
-        <v>0.3687862</v>
+        <v>0.37363865</v>
       </c>
       <c r="N78">
-        <v>2.6212138</v>
+        <v>2.61636135</v>
       </c>
       <c r="O78">
-        <v>0.629091312</v>
+        <v>0.6279267239999999</v>
       </c>
       <c r="P78">
-        <v>1.992122488</v>
+        <v>1.988434626</v>
       </c>
       <c r="Q78">
-        <v>2.262122488</v>
+        <v>2.258434626</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.693710638378888</v>
+        <v>0.7198960849227468</v>
       </c>
       <c r="T78">
-        <v>3.183426109087697</v>
+        <v>3.312084953792594</v>
       </c>
       <c r="U78">
         <v>0.0535</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>8.107678649580706</v>
+        <v>8.002384121664072</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1968842995322318</v>
+        <v>0.1963764458535304</v>
       </c>
       <c r="C79">
-        <v>4.100308512533385</v>
+        <v>4.035336169852609</v>
       </c>
       <c r="D79">
-        <v>10.24520851253338</v>
+        <v>10.27093616985261</v>
       </c>
       <c r="E79">
-        <v>4.6539</v>
+        <v>4.7446</v>
       </c>
       <c r="F79">
-        <v>6.9839</v>
+        <v>7.0746</v>
       </c>
       <c r="G79">
         <v>0.839</v>
@@ -7765,28 +7765,28 @@
         <v>2.99</v>
       </c>
       <c r="M79">
-        <v>0.37363865</v>
+        <v>0.3784911</v>
       </c>
       <c r="N79">
-        <v>2.61636135</v>
+        <v>2.6115089</v>
       </c>
       <c r="O79">
-        <v>0.6279267239999999</v>
+        <v>0.626762136</v>
       </c>
       <c r="P79">
-        <v>1.988434626</v>
+        <v>1.984746764</v>
       </c>
       <c r="Q79">
-        <v>2.258434626</v>
+        <v>2.254746764</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.7198960849227468</v>
+        <v>0.7484620266069564</v>
       </c>
       <c r="T79">
-        <v>3.312084953792594</v>
+        <v>3.452440057107027</v>
       </c>
       <c r="U79">
         <v>0.0535</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>8.002384121664072</v>
+        <v>7.89978945343761</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1963764458535304</v>
+        <v>0.195868592174829</v>
       </c>
       <c r="C80">
-        <v>4.035336169852609</v>
+        <v>3.970493366501765</v>
       </c>
       <c r="D80">
-        <v>10.27093616985261</v>
+        <v>10.29679336650177</v>
       </c>
       <c r="E80">
-        <v>4.7446</v>
+        <v>4.8353</v>
       </c>
       <c r="F80">
-        <v>7.0746</v>
+        <v>7.1653</v>
       </c>
       <c r="G80">
         <v>0.839</v>
@@ -7847,28 +7847,28 @@
         <v>2.99</v>
       </c>
       <c r="M80">
-        <v>0.3784911</v>
+        <v>0.38334355</v>
       </c>
       <c r="N80">
-        <v>2.6115089</v>
+        <v>2.60665645</v>
       </c>
       <c r="O80">
-        <v>0.626762136</v>
+        <v>0.625597548</v>
       </c>
       <c r="P80">
-        <v>1.984746764</v>
+        <v>1.981058902</v>
       </c>
       <c r="Q80">
-        <v>2.254746764</v>
+        <v>2.251058902</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.7484620266069564</v>
+        <v>0.7797485341658525</v>
       </c>
       <c r="T80">
-        <v>3.452440057107027</v>
+        <v>3.606162313118073</v>
       </c>
       <c r="U80">
         <v>0.0535</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>7.89978945343761</v>
+        <v>7.79979211858397</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.195868592174829</v>
+        <v>0.1953607384961276</v>
       </c>
       <c r="C81">
-        <v>3.970493366501765</v>
+        <v>3.905781083300218</v>
       </c>
       <c r="D81">
-        <v>10.29679336650177</v>
+        <v>10.32278108330022</v>
       </c>
       <c r="E81">
-        <v>4.8353</v>
+        <v>4.926</v>
       </c>
       <c r="F81">
-        <v>7.1653</v>
+        <v>7.256</v>
       </c>
       <c r="G81">
         <v>0.839</v>
@@ -7929,28 +7929,28 @@
         <v>2.99</v>
       </c>
       <c r="M81">
-        <v>0.38334355</v>
+        <v>0.388196</v>
       </c>
       <c r="N81">
-        <v>2.60665645</v>
+        <v>2.601804</v>
       </c>
       <c r="O81">
-        <v>0.625597548</v>
+        <v>0.62443296</v>
       </c>
       <c r="P81">
-        <v>1.981058902</v>
+        <v>1.97737104</v>
       </c>
       <c r="Q81">
-        <v>2.251058902</v>
+        <v>2.24737104</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.7797485341658525</v>
+        <v>0.8141636924806385</v>
       </c>
       <c r="T81">
-        <v>3.606162313118073</v>
+        <v>3.775256794730224</v>
       </c>
       <c r="U81">
         <v>0.0535</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>7.79979211858397</v>
+        <v>7.702294717101672</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1953607384961276</v>
+        <v>0.1953453648174263</v>
       </c>
       <c r="C82">
-        <v>3.905781083300218</v>
+        <v>3.815869825768474</v>
       </c>
       <c r="D82">
-        <v>10.32278108330022</v>
+        <v>10.32356982576847</v>
       </c>
       <c r="E82">
-        <v>4.926</v>
+        <v>5.016700000000001</v>
       </c>
       <c r="F82">
-        <v>7.256</v>
+        <v>7.346700000000001</v>
       </c>
       <c r="G82">
         <v>0.839</v>
@@ -8011,45 +8011,45 @@
         <v>2.99</v>
       </c>
       <c r="M82">
-        <v>0.388196</v>
+        <v>0.39892581</v>
       </c>
       <c r="N82">
-        <v>2.601804</v>
+        <v>2.59107419</v>
       </c>
       <c r="O82">
-        <v>0.62443296</v>
+        <v>0.6218578056</v>
       </c>
       <c r="P82">
-        <v>1.97737104</v>
+        <v>1.9692163844</v>
       </c>
       <c r="Q82">
-        <v>2.24737104</v>
+        <v>2.2392163844</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.8141636924806385</v>
+        <v>0.8522014990390859</v>
       </c>
       <c r="T82">
-        <v>3.775256794730224</v>
+        <v>3.962150695459443</v>
       </c>
       <c r="U82">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V82">
         <v>0.24</v>
       </c>
       <c r="W82">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y82">
-        <v>7.702294717101672</v>
+        <v>7.495127978808891</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1953453648174263</v>
+        <v>0.1948435911387249</v>
       </c>
       <c r="C83">
-        <v>3.815869825768474</v>
+        <v>3.750979522215194</v>
       </c>
       <c r="D83">
-        <v>10.32356982576847</v>
+        <v>10.34937952221519</v>
       </c>
       <c r="E83">
-        <v>5.016700000000001</v>
+        <v>5.107400000000001</v>
       </c>
       <c r="F83">
-        <v>7.346700000000001</v>
+        <v>7.437400000000001</v>
       </c>
       <c r="G83">
         <v>0.839</v>
@@ -8093,28 +8093,28 @@
         <v>2.99</v>
       </c>
       <c r="M83">
-        <v>0.39892581</v>
+        <v>0.4038508200000001</v>
       </c>
       <c r="N83">
-        <v>2.59107419</v>
+        <v>2.58614918</v>
       </c>
       <c r="O83">
-        <v>0.6218578056</v>
+        <v>0.6206758032</v>
       </c>
       <c r="P83">
-        <v>1.9692163844</v>
+        <v>1.9654733768</v>
       </c>
       <c r="Q83">
-        <v>2.2392163844</v>
+        <v>2.235473376799999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.8522014990390859</v>
+        <v>0.8944657285484719</v>
       </c>
       <c r="T83">
-        <v>3.962150695459443</v>
+        <v>4.169810585158575</v>
       </c>
       <c r="U83">
         <v>0.0543</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>7.495127978808891</v>
+        <v>7.403723979067319</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1948435911387249</v>
+        <v>0.1943418174600235</v>
       </c>
       <c r="C84">
-        <v>3.750979522215194</v>
+        <v>3.686218594452822</v>
       </c>
       <c r="D84">
-        <v>10.34937952221519</v>
+        <v>10.37531859445282</v>
       </c>
       <c r="E84">
-        <v>5.107400000000001</v>
+        <v>5.198100000000001</v>
       </c>
       <c r="F84">
-        <v>7.437400000000001</v>
+        <v>7.528100000000001</v>
       </c>
       <c r="G84">
         <v>0.839</v>
@@ -8175,28 +8175,28 @@
         <v>2.99</v>
       </c>
       <c r="M84">
-        <v>0.4038508200000001</v>
+        <v>0.4087758300000001</v>
       </c>
       <c r="N84">
-        <v>2.58614918</v>
+        <v>2.58122417</v>
       </c>
       <c r="O84">
-        <v>0.6206758032</v>
+        <v>0.6194938007999999</v>
       </c>
       <c r="P84">
-        <v>1.9654733768</v>
+        <v>1.9617303692</v>
       </c>
       <c r="Q84">
-        <v>2.235473376799999</v>
+        <v>2.2317303692</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.8944657285484719</v>
+        <v>0.94170222035308</v>
       </c>
       <c r="T84">
-        <v>4.169810585158575</v>
+        <v>4.40190105011643</v>
       </c>
       <c r="U84">
         <v>0.0543</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>7.403723979067319</v>
+        <v>7.314522485343616</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1943418174600235</v>
+        <v>0.1938400437813222</v>
       </c>
       <c r="C85">
-        <v>3.686218594452822</v>
+        <v>3.62158801770508</v>
       </c>
       <c r="D85">
-        <v>10.37531859445282</v>
+        <v>10.40138801770508</v>
       </c>
       <c r="E85">
-        <v>5.198100000000001</v>
+        <v>5.288800000000001</v>
       </c>
       <c r="F85">
-        <v>7.528100000000001</v>
+        <v>7.618800000000001</v>
       </c>
       <c r="G85">
         <v>0.839</v>
@@ -8257,28 +8257,28 @@
         <v>2.99</v>
       </c>
       <c r="M85">
-        <v>0.4087758300000001</v>
+        <v>0.4137008400000001</v>
       </c>
       <c r="N85">
-        <v>2.58122417</v>
+        <v>2.57629916</v>
       </c>
       <c r="O85">
-        <v>0.6194938007999999</v>
+        <v>0.6183117983999999</v>
       </c>
       <c r="P85">
-        <v>1.9617303692</v>
+        <v>1.9579873616</v>
       </c>
       <c r="Q85">
-        <v>2.2317303692</v>
+        <v>2.227987361599999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.94170222035308</v>
+        <v>0.9948432736332642</v>
       </c>
       <c r="T85">
-        <v>4.40190105011643</v>
+        <v>4.663002823194016</v>
       </c>
       <c r="U85">
         <v>0.0543</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>7.314522485343616</v>
+        <v>7.227444836708573</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1938400437813222</v>
+        <v>0.1933382701026208</v>
       </c>
       <c r="C86">
-        <v>3.621588017705081</v>
+        <v>3.557088777021908</v>
       </c>
       <c r="D86">
-        <v>10.40138801770508</v>
+        <v>10.42758877702191</v>
       </c>
       <c r="E86">
-        <v>5.2888</v>
+        <v>5.3795</v>
       </c>
       <c r="F86">
-        <v>7.6188</v>
+        <v>7.7095</v>
       </c>
       <c r="G86">
         <v>0.839</v>
@@ -8339,28 +8339,28 @@
         <v>2.99</v>
       </c>
       <c r="M86">
-        <v>0.41370084</v>
+        <v>0.41862585</v>
       </c>
       <c r="N86">
-        <v>2.57629916</v>
+        <v>2.57137415</v>
       </c>
       <c r="O86">
-        <v>0.6183117983999999</v>
+        <v>0.617129796</v>
       </c>
       <c r="P86">
-        <v>1.9579873616</v>
+        <v>1.954244354</v>
       </c>
       <c r="Q86">
-        <v>2.227987361599999</v>
+        <v>2.224244354</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.9948432736332634</v>
+        <v>1.055069800684139</v>
       </c>
       <c r="T86">
-        <v>4.663002823194012</v>
+        <v>4.958918166015277</v>
       </c>
       <c r="U86">
         <v>0.0543</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>7.227444836708574</v>
+        <v>7.142416073923767</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1933382701026208</v>
+        <v>0.1928364964239194</v>
       </c>
       <c r="C87">
-        <v>3.557088777021908</v>
+        <v>3.492721867403553</v>
       </c>
       <c r="D87">
-        <v>10.42758877702191</v>
+        <v>10.45392186740355</v>
       </c>
       <c r="E87">
-        <v>5.3795</v>
+        <v>5.4702</v>
       </c>
       <c r="F87">
-        <v>7.7095</v>
+        <v>7.8002</v>
       </c>
       <c r="G87">
         <v>0.839</v>
@@ -8421,28 +8421,28 @@
         <v>2.99</v>
       </c>
       <c r="M87">
-        <v>0.41862585</v>
+        <v>0.42355086</v>
       </c>
       <c r="N87">
-        <v>2.57137415</v>
+        <v>2.56644914</v>
       </c>
       <c r="O87">
-        <v>0.617129796</v>
+        <v>0.6159477936</v>
       </c>
       <c r="P87">
-        <v>1.954244354</v>
+        <v>1.9505013464</v>
       </c>
       <c r="Q87">
-        <v>2.224244354</v>
+        <v>2.2205013464</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>1.055069800684139</v>
+        <v>1.12390011731371</v>
       </c>
       <c r="T87">
-        <v>4.958918166015277</v>
+        <v>5.297107129239577</v>
       </c>
       <c r="U87">
         <v>0.0543</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>7.142416073923767</v>
+        <v>7.059364724226979</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1928364964239194</v>
+        <v>0.1923347227452181</v>
       </c>
       <c r="C88">
-        <v>3.492721867403553</v>
+        <v>3.42848829392651</v>
       </c>
       <c r="D88">
-        <v>10.45392186740355</v>
+        <v>10.48038829392651</v>
       </c>
       <c r="E88">
-        <v>5.4702</v>
+        <v>5.5609</v>
       </c>
       <c r="F88">
-        <v>7.8002</v>
+        <v>7.8909</v>
       </c>
       <c r="G88">
         <v>0.839</v>
@@ -8503,28 +8503,28 @@
         <v>2.99</v>
       </c>
       <c r="M88">
-        <v>0.42355086</v>
+        <v>0.42847587</v>
       </c>
       <c r="N88">
-        <v>2.56644914</v>
+        <v>2.56152413</v>
       </c>
       <c r="O88">
-        <v>0.6159477936</v>
+        <v>0.6147657912</v>
       </c>
       <c r="P88">
-        <v>1.9505013464</v>
+        <v>1.9467583388</v>
       </c>
       <c r="Q88">
-        <v>2.2205013464</v>
+        <v>2.2167583388</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>1.12390011731371</v>
+        <v>1.203319713424754</v>
       </c>
       <c r="T88">
-        <v>5.297107129239577</v>
+        <v>5.687325163729155</v>
       </c>
       <c r="U88">
         <v>0.0543</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>7.059364724226979</v>
+        <v>6.978222600960002</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1923347227452181</v>
+        <v>0.1918329490665167</v>
       </c>
       <c r="C89">
-        <v>3.42848829392651</v>
+        <v>3.364389071871418</v>
       </c>
       <c r="D89">
-        <v>10.48038829392651</v>
+        <v>10.50698907187142</v>
       </c>
       <c r="E89">
-        <v>5.5609</v>
+        <v>5.6516</v>
       </c>
       <c r="F89">
-        <v>7.8909</v>
+        <v>7.9816</v>
       </c>
       <c r="G89">
         <v>0.839</v>
@@ -8585,28 +8585,28 @@
         <v>2.99</v>
       </c>
       <c r="M89">
-        <v>0.42847587</v>
+        <v>0.43340088</v>
       </c>
       <c r="N89">
-        <v>2.56152413</v>
+        <v>2.55659912</v>
       </c>
       <c r="O89">
-        <v>0.6147657912</v>
+        <v>0.6135837888</v>
       </c>
       <c r="P89">
-        <v>1.9467583388</v>
+        <v>1.9430153312</v>
       </c>
       <c r="Q89">
-        <v>2.2167583388</v>
+        <v>2.213015331199999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.203319713424754</v>
+        <v>1.295975908887639</v>
       </c>
       <c r="T89">
-        <v>5.687325163729155</v>
+        <v>6.142579537300331</v>
       </c>
       <c r="U89">
         <v>0.0543</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>6.978222600960002</v>
+        <v>6.898924616858184</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1918329490665167</v>
+        <v>0.1913311753878154</v>
       </c>
       <c r="C90">
-        <v>3.364389071871418</v>
+        <v>3.300425226852866</v>
       </c>
       <c r="D90">
-        <v>10.50698907187142</v>
+        <v>10.53372522685287</v>
       </c>
       <c r="E90">
-        <v>5.6516</v>
+        <v>5.7423</v>
       </c>
       <c r="F90">
-        <v>7.9816</v>
+        <v>8.0723</v>
       </c>
       <c r="G90">
         <v>0.839</v>
@@ -8667,28 +8667,28 @@
         <v>2.99</v>
       </c>
       <c r="M90">
-        <v>0.43340088</v>
+        <v>0.43832589</v>
       </c>
       <c r="N90">
-        <v>2.55659912</v>
+        <v>2.55167411</v>
       </c>
       <c r="O90">
-        <v>0.6135837888</v>
+        <v>0.6124017864000001</v>
       </c>
       <c r="P90">
-        <v>1.9430153312</v>
+        <v>1.9392723236</v>
       </c>
       <c r="Q90">
-        <v>2.213015331199999</v>
+        <v>2.2092723236</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.295975908887639</v>
+        <v>1.405478685343776</v>
       </c>
       <c r="T90">
-        <v>6.142579537300331</v>
+        <v>6.680607433338991</v>
       </c>
       <c r="U90">
         <v>0.0543</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>6.898924616858184</v>
+        <v>6.821408609927195</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1913311753878154</v>
+        <v>0.190829401709114</v>
       </c>
       <c r="C91">
-        <v>3.300425226852866</v>
+        <v>3.236597794951225</v>
       </c>
       <c r="D91">
-        <v>10.53372522685287</v>
+        <v>10.56059779495122</v>
       </c>
       <c r="E91">
-        <v>5.7423</v>
+        <v>5.833</v>
       </c>
       <c r="F91">
-        <v>8.0723</v>
+        <v>8.163</v>
       </c>
       <c r="G91">
         <v>0.839</v>
@@ -8749,28 +8749,28 @@
         <v>2.99</v>
       </c>
       <c r="M91">
-        <v>0.43832589</v>
+        <v>0.4432509</v>
       </c>
       <c r="N91">
-        <v>2.55167411</v>
+        <v>2.5467491</v>
       </c>
       <c r="O91">
-        <v>0.6124017864000001</v>
+        <v>0.6112197840000001</v>
       </c>
       <c r="P91">
-        <v>1.9392723236</v>
+        <v>1.935529316</v>
       </c>
       <c r="Q91">
-        <v>2.2092723236</v>
+        <v>2.205529316</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.405478685343776</v>
+        <v>1.53688201709114</v>
       </c>
       <c r="T91">
-        <v>6.680607433338991</v>
+        <v>7.326240908585385</v>
       </c>
       <c r="U91">
         <v>0.0543</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>6.821408609927195</v>
+        <v>6.745615180928003</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.190829401709114</v>
+        <v>0.1903276280304126</v>
       </c>
       <c r="C92">
-        <v>3.236597794951225</v>
+        <v>3.172907822846472</v>
       </c>
       <c r="D92">
-        <v>10.56059779495122</v>
+        <v>10.58760782284647</v>
       </c>
       <c r="E92">
-        <v>5.833</v>
+        <v>5.9237</v>
       </c>
       <c r="F92">
-        <v>8.163</v>
+        <v>8.2537</v>
       </c>
       <c r="G92">
         <v>0.839</v>
@@ -8831,28 +8831,28 @@
         <v>2.99</v>
       </c>
       <c r="M92">
-        <v>0.4432509</v>
+        <v>0.44817591</v>
       </c>
       <c r="N92">
-        <v>2.5467491</v>
+        <v>2.54182409</v>
       </c>
       <c r="O92">
-        <v>0.6112197840000001</v>
+        <v>0.6100377816000001</v>
       </c>
       <c r="P92">
-        <v>1.935529316</v>
+        <v>1.9317863084</v>
       </c>
       <c r="Q92">
-        <v>2.205529316</v>
+        <v>2.2017863084</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.53688201709114</v>
+        <v>1.697486089226807</v>
       </c>
       <c r="T92">
-        <v>7.326240908585385</v>
+        <v>8.115348489442088</v>
       </c>
       <c r="U92">
         <v>0.0543</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>6.745615180928003</v>
+        <v>6.671487541577147</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1903276280304126</v>
+        <v>0.1898258543517113</v>
       </c>
       <c r="C93">
-        <v>3.172907822846472</v>
+        <v>3.109356367954092</v>
       </c>
       <c r="D93">
-        <v>10.58760782284647</v>
+        <v>10.61475636795409</v>
       </c>
       <c r="E93">
-        <v>5.9237</v>
+        <v>6.0144</v>
       </c>
       <c r="F93">
-        <v>8.2537</v>
+        <v>8.3444</v>
       </c>
       <c r="G93">
         <v>0.839</v>
@@ -8913,28 +8913,28 @@
         <v>2.99</v>
       </c>
       <c r="M93">
-        <v>0.44817591</v>
+        <v>0.45310092</v>
       </c>
       <c r="N93">
-        <v>2.54182409</v>
+        <v>2.53689908</v>
       </c>
       <c r="O93">
-        <v>0.6100377816000001</v>
+        <v>0.6088557792000001</v>
       </c>
       <c r="P93">
-        <v>1.9317863084</v>
+        <v>1.9280433008</v>
       </c>
       <c r="Q93">
-        <v>2.2017863084</v>
+        <v>2.1980433008</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.697486089226807</v>
+        <v>1.898241179396392</v>
       </c>
       <c r="T93">
-        <v>8.115348489442088</v>
+        <v>9.101732965512969</v>
       </c>
       <c r="U93">
         <v>0.0543</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>6.671487541577147</v>
+        <v>6.59897137264696</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1898258543517113</v>
+        <v>0.1893240806730099</v>
       </c>
       <c r="C94">
-        <v>3.109356367954092</v>
+        <v>3.045944498563077</v>
       </c>
       <c r="D94">
-        <v>10.61475636795409</v>
+        <v>10.64204449856308</v>
       </c>
       <c r="E94">
-        <v>6.0144</v>
+        <v>6.1051</v>
       </c>
       <c r="F94">
-        <v>8.3444</v>
+        <v>8.4351</v>
       </c>
       <c r="G94">
         <v>0.839</v>
@@ -8995,28 +8995,28 @@
         <v>2.99</v>
       </c>
       <c r="M94">
-        <v>0.45310092</v>
+        <v>0.45802593</v>
       </c>
       <c r="N94">
-        <v>2.53689908</v>
+        <v>2.53197407</v>
       </c>
       <c r="O94">
-        <v>0.6088557792000001</v>
+        <v>0.6076737768000001</v>
       </c>
       <c r="P94">
-        <v>1.9280433008</v>
+        <v>1.9243002932</v>
       </c>
       <c r="Q94">
-        <v>2.1980433008</v>
+        <v>2.1943002932</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.898241179396392</v>
+        <v>2.156354866757285</v>
       </c>
       <c r="T94">
-        <v>9.101732965512969</v>
+        <v>10.3699415776041</v>
       </c>
       <c r="U94">
         <v>0.0543</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>6.59897137264696</v>
+        <v>6.528014691220648</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1893240806730099</v>
+        <v>0.1888223069943085</v>
       </c>
       <c r="C95">
-        <v>3.045944498563077</v>
+        <v>2.982673293976045</v>
       </c>
       <c r="D95">
-        <v>10.64204449856308</v>
+        <v>10.66947329397605</v>
       </c>
       <c r="E95">
-        <v>6.1051</v>
+        <v>6.1958</v>
       </c>
       <c r="F95">
-        <v>8.4351</v>
+        <v>8.5258</v>
       </c>
       <c r="G95">
         <v>0.839</v>
@@ -9077,28 +9077,28 @@
         <v>2.99</v>
       </c>
       <c r="M95">
-        <v>0.45802593</v>
+        <v>0.46295094</v>
       </c>
       <c r="N95">
-        <v>2.53197407</v>
+        <v>2.52704906</v>
       </c>
       <c r="O95">
-        <v>0.6076737768000001</v>
+        <v>0.6064917744000001</v>
       </c>
       <c r="P95">
-        <v>1.9243002932</v>
+        <v>1.9205572856</v>
       </c>
       <c r="Q95">
-        <v>2.1943002932</v>
+        <v>2.1905572856</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>2.156354866757285</v>
+        <v>2.500506449905144</v>
       </c>
       <c r="T95">
-        <v>10.3699415776041</v>
+        <v>12.06088639372561</v>
       </c>
       <c r="U95">
         <v>0.0543</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>6.528014691220648</v>
+        <v>6.458567726420428</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1888223069943085</v>
+        <v>0.1883205333156071</v>
       </c>
       <c r="C96">
-        <v>2.982673293976045</v>
+        <v>2.919543844651537</v>
       </c>
       <c r="D96">
-        <v>10.66947329397605</v>
+        <v>10.69704384465154</v>
       </c>
       <c r="E96">
-        <v>6.1958</v>
+        <v>6.2865</v>
       </c>
       <c r="F96">
-        <v>8.5258</v>
+        <v>8.6165</v>
       </c>
       <c r="G96">
         <v>0.839</v>
@@ -9159,28 +9159,28 @@
         <v>2.99</v>
       </c>
       <c r="M96">
-        <v>0.46295094</v>
+        <v>0.46787595</v>
       </c>
       <c r="N96">
-        <v>2.52704906</v>
+        <v>2.52212405</v>
       </c>
       <c r="O96">
-        <v>0.6064917744000001</v>
+        <v>0.605309772</v>
       </c>
       <c r="P96">
-        <v>1.9205572856</v>
+        <v>1.916814278</v>
       </c>
       <c r="Q96">
-        <v>2.1905572856</v>
+        <v>2.186814278</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.500506449905144</v>
+        <v>2.982318666312147</v>
       </c>
       <c r="T96">
-        <v>12.06088639372561</v>
+        <v>14.42820913629573</v>
       </c>
       <c r="U96">
         <v>0.0543</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>6.458567726420428</v>
+        <v>6.390582802984424</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1883205333156071</v>
+        <v>0.1878187596369057</v>
       </c>
       <c r="C97">
-        <v>2.919543844651537</v>
+        <v>2.856557252348543</v>
       </c>
       <c r="D97">
-        <v>10.69704384465154</v>
+        <v>10.72475725234854</v>
       </c>
       <c r="E97">
-        <v>6.2865</v>
+        <v>6.3772</v>
       </c>
       <c r="F97">
-        <v>8.6165</v>
+        <v>8.7072</v>
       </c>
       <c r="G97">
         <v>0.839</v>
@@ -9241,28 +9241,28 @@
         <v>2.99</v>
       </c>
       <c r="M97">
-        <v>0.46787595</v>
+        <v>0.47280096</v>
       </c>
       <c r="N97">
-        <v>2.52212405</v>
+        <v>2.51719904</v>
       </c>
       <c r="O97">
-        <v>0.605309772</v>
+        <v>0.6041277696</v>
       </c>
       <c r="P97">
-        <v>1.916814278</v>
+        <v>1.9130712704</v>
       </c>
       <c r="Q97">
-        <v>2.186814278</v>
+        <v>2.1830712704</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.982318666312147</v>
+        <v>3.70503699092265</v>
       </c>
       <c r="T97">
-        <v>14.42820913629573</v>
+        <v>17.9791932501509</v>
       </c>
       <c r="U97">
         <v>0.0543</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>6.390582802984424</v>
+        <v>6.324014232120002</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1878187596369058</v>
+        <v>0.1873169859582044</v>
       </c>
       <c r="C98">
-        <v>2.856557252348541</v>
+        <v>2.793714630273236</v>
       </c>
       <c r="D98">
-        <v>10.72475725234854</v>
+        <v>10.75261463027324</v>
       </c>
       <c r="E98">
-        <v>6.3772</v>
+        <v>6.4679</v>
       </c>
       <c r="F98">
-        <v>8.7072</v>
+        <v>8.7979</v>
       </c>
       <c r="G98">
         <v>0.839</v>
@@ -9323,28 +9323,28 @@
         <v>2.99</v>
       </c>
       <c r="M98">
-        <v>0.47280096</v>
+        <v>0.47772597</v>
       </c>
       <c r="N98">
-        <v>2.51719904</v>
+        <v>2.51227403</v>
       </c>
       <c r="O98">
-        <v>0.6041277696</v>
+        <v>0.6029457672</v>
       </c>
       <c r="P98">
-        <v>1.9130712704</v>
+        <v>1.9093282628</v>
       </c>
       <c r="Q98">
-        <v>2.1830712704</v>
+        <v>2.1793282628</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>3.705036990922641</v>
+        <v>4.909567531940143</v>
       </c>
       <c r="T98">
-        <v>17.97919325015085</v>
+        <v>23.89750010657611</v>
       </c>
       <c r="U98">
         <v>0.0543</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>6.324014232120002</v>
+        <v>6.258818209108457</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1873169859582044</v>
+        <v>0.186815212279503</v>
       </c>
       <c r="C99">
-        <v>2.793714630273236</v>
+        <v>2.731017103228075</v>
       </c>
       <c r="D99">
-        <v>10.75261463027324</v>
+        <v>10.78061710322807</v>
       </c>
       <c r="E99">
-        <v>6.4679</v>
+        <v>6.5586</v>
       </c>
       <c r="F99">
-        <v>8.7979</v>
+        <v>8.8886</v>
       </c>
       <c r="G99">
         <v>0.839</v>
@@ -9405,28 +9405,28 @@
         <v>2.99</v>
       </c>
       <c r="M99">
-        <v>0.47772597</v>
+        <v>0.48265098</v>
       </c>
       <c r="N99">
-        <v>2.51227403</v>
+        <v>2.50734902</v>
       </c>
       <c r="O99">
-        <v>0.6029457672</v>
+        <v>0.6017637648</v>
       </c>
       <c r="P99">
-        <v>1.9093282628</v>
+        <v>1.9055852552</v>
       </c>
       <c r="Q99">
-        <v>2.1793282628</v>
+        <v>2.1755852552</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>4.909567531940143</v>
+        <v>7.318628613975144</v>
       </c>
       <c r="T99">
-        <v>23.89750010657611</v>
+        <v>35.73411381942663</v>
       </c>
       <c r="U99">
         <v>0.0543</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>6.258818209108457</v>
+        <v>6.194952717178778</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.186815212279503</v>
+        <v>0.1863134386008017</v>
       </c>
       <c r="C100">
-        <v>2.731017103228075</v>
+        <v>2.668465807763145</v>
       </c>
       <c r="D100">
-        <v>10.78061710322807</v>
+        <v>10.80876580776314</v>
       </c>
       <c r="E100">
-        <v>6.5586</v>
+        <v>6.6493</v>
       </c>
       <c r="F100">
-        <v>8.8886</v>
+        <v>8.9793</v>
       </c>
       <c r="G100">
         <v>0.839</v>
@@ -9487,28 +9487,28 @@
         <v>2.99</v>
       </c>
       <c r="M100">
-        <v>0.48265098</v>
+        <v>0.48757599</v>
       </c>
       <c r="N100">
-        <v>2.50734902</v>
+        <v>2.50242401</v>
       </c>
       <c r="O100">
-        <v>0.6017637648</v>
+        <v>0.6005817624000001</v>
       </c>
       <c r="P100">
-        <v>1.9055852552</v>
+        <v>1.9018422476</v>
       </c>
       <c r="Q100">
-        <v>2.1755852552</v>
+        <v>2.1718422476</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>7.318628613975144</v>
+        <v>14.54581186008015</v>
       </c>
       <c r="T100">
-        <v>35.73411381942663</v>
+        <v>71.24395495797822</v>
       </c>
       <c r="U100">
         <v>0.0543</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>6.194952717178778</v>
+        <v>6.132377437207276</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1863134386008017</v>
-      </c>
-      <c r="C101">
-        <v>2.668465807763145</v>
-      </c>
-      <c r="D101">
-        <v>10.80876580776314</v>
-      </c>
-      <c r="E101">
-        <v>6.6493</v>
-      </c>
-      <c r="F101">
-        <v>8.9793</v>
-      </c>
-      <c r="G101">
-        <v>0.839</v>
-      </c>
-      <c r="H101">
-        <v>6.74</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3.26</v>
-      </c>
-      <c r="K101">
-        <v>0.2699999999999996</v>
-      </c>
-      <c r="L101">
-        <v>2.99</v>
-      </c>
-      <c r="M101">
-        <v>0.48757599</v>
-      </c>
-      <c r="N101">
-        <v>2.50242401</v>
-      </c>
-      <c r="O101">
-        <v>0.6005817624000001</v>
-      </c>
-      <c r="P101">
-        <v>1.9018422476</v>
-      </c>
-      <c r="Q101">
-        <v>2.1718422476</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>14.54581186008015</v>
-      </c>
-      <c r="T101">
-        <v>71.24395495797822</v>
-      </c>
-      <c r="U101">
-        <v>0.0543</v>
-      </c>
-      <c r="V101">
-        <v>0.24</v>
-      </c>
-      <c r="W101">
-        <v>0.041268</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A2/A</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>6.132377437207276</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
